--- a/Treinamento/Planilha Robô Regularizar.xlsx
+++ b/Treinamento/Planilha Robô Regularizar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28502"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="211" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98DB5E54-C398-49CC-AA28-41D773187DCF}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C95E9433-9EAF-4EC3-9B54-F57AFB64B025}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="4">
   <si>
     <t>Recibo</t>
   </si>
@@ -467,7 +467,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>666089440</v>
+        <v>728494604</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>708939156</v>
+        <v>604302418</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>715868729</v>
+        <v>611567615</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>708941806</v>
+        <v>617150804</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>701802419</v>
+        <v>615098609</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>663802951</v>
+        <v>612850424</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>633670116</v>
+        <v>602333720</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>647453517</v>
+        <v>569161536</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>648223281</v>
+        <v>590170928</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>610916060</v>
+        <v>593839370</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>609349927</v>
+        <v>583866888</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>606413718</v>
+        <v>582715029</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>604558654</v>
+        <v>579472709</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>597976764</v>
+        <v>576958726</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>601981685</v>
+        <v>574335687</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
@@ -587,7 +587,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>601540762</v>
+        <v>564991283</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -595,7 +595,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>595547005</v>
+        <v>531048084</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>590749010</v>
+        <v>545604393</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>589775455</v>
+        <v>551197753</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
@@ -619,7 +619,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>588734438</v>
+        <v>550459543</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
@@ -627,7 +627,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>582347286</v>
+        <v>174328785</v>
       </c>
       <c r="B22" t="s">
         <v>2</v>
@@ -635,7 +635,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>581480096</v>
+        <v>525245506</v>
       </c>
       <c r="B23" t="s">
         <v>2</v>
@@ -643,7 +643,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>581065442</v>
+        <v>172801478</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>580775355</v>
+        <v>172265260</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>543545473</v>
+        <v>641510973</v>
       </c>
       <c r="B26" t="s">
         <v>2</v>
@@ -667,7 +667,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>173645445</v>
+        <v>638901003</v>
       </c>
       <c r="B27" t="s">
         <v>2</v>
@@ -675,7 +675,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>543543759</v>
+        <v>627274206</v>
       </c>
       <c r="B28" t="s">
         <v>2</v>
@@ -683,7 +683,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>543260057</v>
+        <v>625957802</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
@@ -691,7 +691,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>529324240</v>
+        <v>695695258</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>174056816</v>
+        <v>712775042</v>
       </c>
       <c r="B31" t="s">
         <v>2</v>
@@ -707,81 +707,225 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>702625744</v>
+        <v>693899027</v>
       </c>
       <c r="B32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>726840089</v>
+        <v>692890563</v>
       </c>
       <c r="B33" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>602122115</v>
+        <v>690858166</v>
       </c>
       <c r="B34" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>649860537</v>
+        <v>677678355</v>
       </c>
       <c r="B35" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>668862281</v>
+        <v>662848120</v>
       </c>
       <c r="B36" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>693805669</v>
+        <v>663993636</v>
       </c>
       <c r="B37" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>672471319</v>
+        <v>667944320</v>
       </c>
       <c r="B38" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>628100772</v>
+        <v>649304429</v>
       </c>
       <c r="B39" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>623380262</v>
+        <v>728395132</v>
       </c>
       <c r="B40" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>609090265</v>
+        <v>726573334</v>
       </c>
       <c r="B41" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>727263943</v>
+      </c>
+      <c r="B42" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>624805515</v>
+      </c>
+      <c r="B43" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>635962628</v>
+      </c>
+      <c r="B44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>631275827</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>630949174</v>
+      </c>
+      <c r="B46" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>629225032</v>
+      </c>
+      <c r="B47" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>563495567</v>
+      </c>
+      <c r="B48" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>171864006</v>
+      </c>
+      <c r="B49" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>723932632</v>
+      </c>
+      <c r="B50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>674694942</v>
+      </c>
+      <c r="B51" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>697181968</v>
+      </c>
+      <c r="B52" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>705928798</v>
+      </c>
+      <c r="B53" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>702023122</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>697664542</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>677917357</v>
+      </c>
+      <c r="B56" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>672757865</v>
+      </c>
+      <c r="B57" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>643652922</v>
+      </c>
+      <c r="B58" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>727547956</v>
+      </c>
+      <c r="B59" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Treinamento/Planilha Robô Regularizar.xlsx
+++ b/Treinamento/Planilha Robô Regularizar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28512"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE04210-R0261133\ICM\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BD65D2-2615-43D9-9064-58A8B720A3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="235" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F92369A-ED52-4C69-848C-36BB6B6172E8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
+    <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="4">
   <si>
     <t>Recibo</t>
   </si>
@@ -54,7 +54,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -451,13 +451,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDA9D80-CE6D-4C1A-B019-EB3A00964886}">
   <dimension ref="A1:B543"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" customWidth="1"/>
-    <col min="2" max="2" width="51.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="51.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -465,2063 +465,2407 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
-        <v>580611287</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
-        <v>625980002</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
-        <v>689182552</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
-        <v>705057440</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
-        <v>701963591</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
-        <v>700912706</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
-        <v>690233816</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
-        <v>659303618</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
-        <v>679035133</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
-        <v>666230325</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
-        <v>620407233</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
-        <v>617835479</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
-        <v>610973863</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
-        <v>616112490</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3">
-        <v>614005944</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="3">
-        <v>609815794</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="3">
-        <v>606312100</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="3">
-        <v>605272248</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="3">
-        <v>602095097</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="3">
-        <v>601852605</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="3">
-        <v>600745537</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="3">
-        <v>599239179</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="3">
-        <v>596836563</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
-        <v>594835765</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="3">
-        <v>588734446</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="3">
-        <v>587221429</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="3">
-        <v>550974145</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="3">
-        <v>546155635</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="3">
-        <v>528480084</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="3">
-        <v>172801957</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="3">
-        <v>707186825</v>
-      </c>
-      <c r="B32" s="3" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>643305075</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>715172049</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>734439767</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>715869263</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>715868836</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>671901704</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>681207811</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>678944848</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>544743705</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>597078850</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>596263073</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>587424619</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>584796241</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>583741214</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>581631490</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>576761682</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>547141683</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>572914244</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>568224335</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>561861588</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>550774412</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>548201932</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>545334694</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>173968227</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>170345619</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>653491146</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>665018515</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>657536169</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>659614170</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>658954650</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>644885695</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>636072302</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>616790626</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>605126238</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>609873504</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>608707216</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>606543670</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>613190200</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>610122651</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>610862173</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>594432365</v>
+      </c>
+      <c r="B42" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>637452412</v>
+      </c>
+      <c r="B43" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>635739273</v>
+      </c>
+      <c r="B44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>630843252</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>170977783</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>737077457</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>732959816</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>687239735</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>699478289</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>723632539</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>587082896</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>653549034</v>
+      </c>
+      <c r="B53" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>628213468</v>
+      </c>
+      <c r="B54" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>627714896</v>
+      </c>
+      <c r="B55" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>611939483</v>
+      </c>
+      <c r="B56" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>611654496</v>
+      </c>
+      <c r="B57" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>611318001</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>609367226</v>
+      </c>
+      <c r="B59" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>608130153</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>603734355</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>603647706</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>599518580</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>585415239</v>
+      </c>
+      <c r="B64" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>583104611</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>576216786</v>
+      </c>
+      <c r="B66" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>551003704</v>
+      </c>
+      <c r="B67" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>536331873</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>521913552</v>
+      </c>
+      <c r="B69" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>490674573</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>734760980</v>
+      </c>
+      <c r="B71" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>733657245</v>
+      </c>
+      <c r="B72" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>660533419</v>
+      </c>
+      <c r="B73" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>613216062</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>639784036</v>
+      </c>
+      <c r="B75" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="15">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
     </row>
-    <row r="92" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" ht="15">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
     </row>
-    <row r="93" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" ht="15">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
     </row>
-    <row r="94" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" ht="15">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
     </row>
-    <row r="95" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" ht="15">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
     </row>
-    <row r="96" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" ht="15">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
     </row>
-    <row r="97" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" ht="15">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
     </row>
-    <row r="98" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" ht="15">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
     </row>
-    <row r="99" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" ht="15">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
     </row>
-    <row r="100" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" ht="15">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
     </row>
-    <row r="101" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" ht="15">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
     </row>
-    <row r="102" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" ht="15">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
     </row>
-    <row r="103" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" ht="15">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
     </row>
-    <row r="104" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" ht="15">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
     </row>
-    <row r="105" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" ht="15">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
     </row>
-    <row r="106" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" ht="15">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
     </row>
-    <row r="107" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" ht="15">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" ht="15">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
     </row>
-    <row r="109" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" ht="15">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
     </row>
-    <row r="110" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" ht="15">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
     </row>
-    <row r="111" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" ht="15">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
     </row>
-    <row r="112" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:2" ht="15">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
     </row>
-    <row r="113" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" ht="15">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
     </row>
-    <row r="114" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" ht="15">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
     </row>
-    <row r="115" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" ht="15">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
     </row>
-    <row r="116" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" ht="15">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
     </row>
-    <row r="117" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" ht="15">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
     </row>
-    <row r="118" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" ht="15">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
     </row>
-    <row r="119" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" ht="15">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
     </row>
-    <row r="120" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" ht="15">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
     </row>
-    <row r="121" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" ht="15">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
     </row>
-    <row r="122" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" ht="15">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
     </row>
-    <row r="123" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" ht="15">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
     </row>
-    <row r="124" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" ht="15">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
     </row>
-    <row r="125" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" ht="15">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
     </row>
-    <row r="126" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" ht="15">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
     </row>
-    <row r="127" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" ht="15">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
     </row>
-    <row r="128" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" ht="15">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
     </row>
-    <row r="129" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" ht="15">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
     </row>
-    <row r="130" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" ht="15">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
     </row>
-    <row r="131" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" ht="15">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
     </row>
-    <row r="132" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" ht="15">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
     </row>
-    <row r="133" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" ht="15">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
     </row>
-    <row r="134" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" ht="15">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
     </row>
-    <row r="135" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" ht="15">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
     </row>
-    <row r="136" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" ht="15">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
     </row>
-    <row r="137" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" ht="15">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
     </row>
-    <row r="138" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" ht="15">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
     </row>
-    <row r="139" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" ht="15">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
     </row>
-    <row r="140" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" ht="15">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
     </row>
-    <row r="141" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" ht="15">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
     </row>
-    <row r="142" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" ht="15">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
     </row>
-    <row r="143" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:2" ht="15">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
     </row>
-    <row r="144" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" ht="15">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
     </row>
-    <row r="145" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" ht="15">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
     </row>
-    <row r="146" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" ht="15">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
     </row>
-    <row r="147" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" ht="15">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
     </row>
-    <row r="148" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:2" ht="15">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
     </row>
-    <row r="149" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:2" ht="15">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
     </row>
-    <row r="150" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:2" ht="15">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
     </row>
-    <row r="151" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:2" ht="15">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
     </row>
-    <row r="152" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:2" ht="15">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
     </row>
-    <row r="153" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:2" ht="15">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
     </row>
-    <row r="154" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:2" ht="15">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
     </row>
-    <row r="155" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:2" ht="15">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
     </row>
-    <row r="156" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:2" ht="15">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
     </row>
-    <row r="157" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:2" ht="15">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
     </row>
-    <row r="158" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:2" ht="15">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
     </row>
-    <row r="159" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:2" ht="15">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
     </row>
-    <row r="160" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:2" ht="15">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
     </row>
-    <row r="161" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:2" ht="15">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
     </row>
-    <row r="162" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:2" ht="15">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
     </row>
-    <row r="163" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:2" ht="15">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
     </row>
-    <row r="164" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:2" ht="15">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
     </row>
-    <row r="165" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:2" ht="15">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
     </row>
-    <row r="166" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:2" ht="15">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
     </row>
-    <row r="167" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:2" ht="15">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
     </row>
-    <row r="168" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:2" ht="15">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
     </row>
-    <row r="169" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:2" ht="15">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
     </row>
-    <row r="170" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:2" ht="15">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
     </row>
-    <row r="171" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:2" ht="15">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
     </row>
-    <row r="172" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:2" ht="15">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
     </row>
-    <row r="173" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:2" ht="15">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
     </row>
-    <row r="174" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:2" ht="15">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
     </row>
-    <row r="175" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:2" ht="15">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
     </row>
-    <row r="176" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:2" ht="15">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
     </row>
-    <row r="177" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:2" ht="15">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
     </row>
-    <row r="178" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:2" ht="15">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
     </row>
-    <row r="179" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:2" ht="15">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
     </row>
-    <row r="180" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:2" ht="15">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
     </row>
-    <row r="181" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:2" ht="15">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
     </row>
-    <row r="182" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:2" ht="15">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
     </row>
-    <row r="183" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:2" ht="15">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
     </row>
-    <row r="184" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:2" ht="15">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
     </row>
-    <row r="185" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:2" ht="15">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
     </row>
-    <row r="186" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:2" ht="15">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
     </row>
-    <row r="187" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:2" ht="15">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
     </row>
-    <row r="188" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:2" ht="15">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
     </row>
-    <row r="189" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:2" ht="15">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
     </row>
-    <row r="190" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:2" ht="15">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
     </row>
-    <row r="191" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:2" ht="15">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
     </row>
-    <row r="192" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:2" ht="15">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
     </row>
-    <row r="193" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:2" ht="15">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
     </row>
-    <row r="194" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:2" ht="15">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
     </row>
-    <row r="195" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:2" ht="15">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
     </row>
-    <row r="196" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:2" ht="15">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
     </row>
-    <row r="197" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:2" ht="15">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
     </row>
-    <row r="198" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:2" ht="15">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
     </row>
-    <row r="199" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:2" ht="15">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
     </row>
-    <row r="200" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:2" ht="15">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
     </row>
-    <row r="201" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:2" ht="15">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
     </row>
-    <row r="202" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:2" ht="15">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
     </row>
-    <row r="203" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:2" ht="15">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
     </row>
-    <row r="204" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:2" ht="15">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
     </row>
-    <row r="205" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:2" ht="15">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
     </row>
-    <row r="206" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:2" ht="15">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
     </row>
-    <row r="207" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:2" ht="15">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
     </row>
-    <row r="208" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:2" ht="15">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
     </row>
-    <row r="209" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:2" ht="15">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
     </row>
-    <row r="210" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:2" ht="15">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
     </row>
-    <row r="211" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:2" ht="15">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
     </row>
-    <row r="212" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:2" ht="15">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
     </row>
-    <row r="213" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:2" ht="15">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
     </row>
-    <row r="214" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:2" ht="15">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
     </row>
-    <row r="215" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:2" ht="15">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
     </row>
-    <row r="216" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:2" ht="15">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
     </row>
-    <row r="217" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:2" ht="15">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
     </row>
-    <row r="218" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:2" ht="15">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
     </row>
-    <row r="219" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:2" ht="15">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
     </row>
-    <row r="220" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:2" ht="15">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
     </row>
-    <row r="221" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:2" ht="15">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
     </row>
-    <row r="222" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:2" ht="15">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
     </row>
-    <row r="223" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:2" ht="15">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
     </row>
-    <row r="224" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:2" ht="15">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
     </row>
-    <row r="225" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:2" ht="15">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
     </row>
-    <row r="226" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:2" ht="15">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
     </row>
-    <row r="227" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:2" ht="15">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
     </row>
-    <row r="228" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:2" ht="15">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
     </row>
-    <row r="229" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:2" ht="15">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
     </row>
-    <row r="230" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:2" ht="15">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
     </row>
-    <row r="231" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:2" ht="15">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
     </row>
-    <row r="232" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:2" ht="15">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
     </row>
-    <row r="233" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:2" ht="15">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
     </row>
-    <row r="234" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:2" ht="15">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
     </row>
-    <row r="235" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:2" ht="15">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
     </row>
-    <row r="236" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:2" ht="15">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
     </row>
-    <row r="237" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:2" ht="15">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
     </row>
-    <row r="238" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:2" ht="15">
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
     </row>
-    <row r="239" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:2" ht="15">
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
     </row>
-    <row r="240" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:2" ht="15">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
     </row>
-    <row r="241" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:2" ht="15">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
     </row>
-    <row r="242" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:2" ht="15">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
     </row>
-    <row r="243" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:2" ht="15">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
     </row>
-    <row r="244" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:2" ht="15">
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
     </row>
-    <row r="245" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:2" ht="15">
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
     </row>
-    <row r="246" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:2" ht="15">
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
     </row>
-    <row r="247" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:2" ht="15">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
     </row>
-    <row r="248" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:2" ht="15">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
     </row>
-    <row r="249" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:2" ht="15">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
     </row>
-    <row r="250" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:2" ht="15">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
     </row>
-    <row r="251" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:2" ht="15">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
     </row>
-    <row r="252" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:2" ht="15">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
     </row>
-    <row r="253" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:2" ht="15">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
     </row>
-    <row r="254" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:2" ht="15">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
     </row>
-    <row r="255" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:2" ht="15">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
     </row>
-    <row r="256" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:2" ht="15">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
     </row>
-    <row r="257" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:2" ht="15">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
     </row>
-    <row r="258" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:2" ht="15">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
     </row>
-    <row r="259" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:2" ht="15">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
     </row>
-    <row r="260" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:2" ht="15">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
     </row>
-    <row r="261" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:2" ht="15">
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
     </row>
-    <row r="262" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:2" ht="15">
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
     </row>
-    <row r="263" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:2" ht="15">
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
     </row>
-    <row r="264" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:2" ht="15">
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
     </row>
-    <row r="265" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:2" ht="15">
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
     </row>
-    <row r="266" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:2" ht="15">
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
     </row>
-    <row r="267" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:2" ht="15">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
     </row>
-    <row r="268" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:2" ht="15">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
     </row>
-    <row r="269" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:2" ht="15">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
     </row>
-    <row r="270" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:2" ht="15">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
     </row>
-    <row r="271" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:2" ht="15">
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
     </row>
-    <row r="272" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:2" ht="15">
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
     </row>
-    <row r="273" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:2" ht="15">
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
     </row>
-    <row r="274" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:2" ht="15">
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
     </row>
-    <row r="275" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:2" ht="15">
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
     </row>
-    <row r="276" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:2" ht="15">
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
     </row>
-    <row r="277" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:2" ht="15">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
     </row>
-    <row r="278" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:2" ht="15">
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
     </row>
-    <row r="279" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:2" ht="15">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
     </row>
-    <row r="280" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:2" ht="15">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
     </row>
-    <row r="281" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:2" ht="15">
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
     </row>
-    <row r="282" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:2" ht="15">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
     </row>
-    <row r="283" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:2" ht="15">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
     </row>
-    <row r="284" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:2" ht="15">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
     </row>
-    <row r="285" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:2" ht="15">
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
     </row>
-    <row r="286" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:2" ht="15">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
     </row>
-    <row r="287" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:2" ht="15">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
     </row>
-    <row r="288" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:2" ht="15">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
     </row>
-    <row r="289" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:2" ht="15">
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
     </row>
-    <row r="290" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:2" ht="15">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
     </row>
-    <row r="291" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:2" ht="15">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
     </row>
-    <row r="292" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:2" ht="15">
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
     </row>
-    <row r="293" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:2" ht="15">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
     </row>
-    <row r="294" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:2" ht="15">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
     </row>
-    <row r="295" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:2" ht="15">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
     </row>
-    <row r="296" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:2" ht="15">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
     </row>
-    <row r="297" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:2" ht="15">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
     </row>
-    <row r="298" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:2" ht="15">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
     </row>
-    <row r="299" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:2" ht="15">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
     </row>
-    <row r="300" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:2" ht="15">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
     </row>
-    <row r="301" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:2" ht="15">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
     </row>
-    <row r="302" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:2" ht="15">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
     </row>
-    <row r="303" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:2" ht="15">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
     </row>
-    <row r="304" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:2" ht="15">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
     </row>
-    <row r="305" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:2" ht="15">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
     </row>
-    <row r="306" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:2" ht="15">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
     </row>
-    <row r="307" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:2" ht="15">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
     </row>
-    <row r="308" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:2" ht="15">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
     </row>
-    <row r="309" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:2" ht="15">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
     </row>
-    <row r="310" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:2" ht="15">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
     </row>
-    <row r="311" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:2" ht="15">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
     </row>
-    <row r="312" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:2" ht="15">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
     </row>
-    <row r="313" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:2" ht="15">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
     </row>
-    <row r="314" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:2" ht="15">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
     </row>
-    <row r="315" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:2" ht="15">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
     </row>
-    <row r="316" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:2" ht="15">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
     </row>
-    <row r="317" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:2" ht="15">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
     </row>
-    <row r="318" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:2" ht="15">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
     </row>
-    <row r="319" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:2" ht="15">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
     </row>
-    <row r="320" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:2" ht="15">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
     </row>
-    <row r="321" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:2" ht="15">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
     </row>
-    <row r="322" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:2" ht="15">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
     </row>
-    <row r="323" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:2" ht="15">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
     </row>
-    <row r="324" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:2" ht="15">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
     </row>
-    <row r="325" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:2" ht="15">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
     </row>
-    <row r="326" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:2" ht="15">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
     </row>
-    <row r="327" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:2" ht="15">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
     </row>
-    <row r="328" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:2" ht="15">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
     </row>
-    <row r="329" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:2" ht="15">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
     </row>
-    <row r="330" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:2" ht="15">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
     </row>
-    <row r="331" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:2" ht="15">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
     </row>
-    <row r="332" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:2" ht="15">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
     </row>
-    <row r="333" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:2" ht="15">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
     </row>
-    <row r="334" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:2" ht="15">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
     </row>
-    <row r="335" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:2" ht="15">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
     </row>
-    <row r="336" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:2" ht="15">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
     </row>
-    <row r="337" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:2" ht="15">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
     </row>
-    <row r="338" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:2" ht="15">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
     </row>
-    <row r="339" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:2" ht="15">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
     </row>
-    <row r="340" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:2" ht="15">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
     </row>
-    <row r="341" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:2" ht="15">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
     </row>
-    <row r="342" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:2" ht="15">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
     </row>
-    <row r="343" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:2" ht="15">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
     </row>
-    <row r="344" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:2" ht="15">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
     </row>
-    <row r="345" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:2" ht="15">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
     </row>
-    <row r="346" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:2" ht="15">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
     </row>
-    <row r="347" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:2" ht="15">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
     </row>
-    <row r="348" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:2" ht="15">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
     </row>
-    <row r="349" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:2" ht="15">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
     </row>
-    <row r="350" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:2" ht="15">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
     </row>
-    <row r="351" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:2" ht="15">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
     </row>
-    <row r="352" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:2" ht="15">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
     </row>
-    <row r="353" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:2" ht="15">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
     </row>
-    <row r="354" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:2" ht="15">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
     </row>
-    <row r="355" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:2" ht="15">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
     </row>
-    <row r="356" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:2" ht="15">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
     </row>
-    <row r="357" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:2" ht="15">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
     </row>
-    <row r="358" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:2" ht="15">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
     </row>
-    <row r="359" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:2" ht="15">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
     </row>
-    <row r="360" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:2" ht="15">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
     </row>
-    <row r="361" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:2" ht="15">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
     </row>
-    <row r="362" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:2" ht="15">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
     </row>
-    <row r="363" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:2" ht="15">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
     </row>
-    <row r="364" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:2" ht="15">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
     </row>
-    <row r="365" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:2" ht="15">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
     </row>
-    <row r="366" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:2" ht="15">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
     </row>
-    <row r="367" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:2" ht="15">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
     </row>
-    <row r="368" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:2" ht="15">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
     </row>
-    <row r="369" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:2" ht="15">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
     </row>
-    <row r="370" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:2" ht="15">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
     </row>
-    <row r="371" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:2" ht="15">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
     </row>
-    <row r="372" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:2" ht="15">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
     </row>
-    <row r="373" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:2" ht="15">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
     </row>
-    <row r="374" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:2" ht="15">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
     </row>
-    <row r="375" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:2" ht="15">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
     </row>
-    <row r="376" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:2" ht="15">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
     </row>
-    <row r="377" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:2" ht="15">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
     </row>
-    <row r="378" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:2" ht="15">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
     </row>
-    <row r="379" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:2" ht="15">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
     </row>
-    <row r="380" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:2" ht="15">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
     </row>
-    <row r="381" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:2" ht="15">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
     </row>
-    <row r="382" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:2" ht="15">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
     </row>
-    <row r="383" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:2" ht="15">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
     </row>
-    <row r="384" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:2" ht="15">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
     </row>
-    <row r="385" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:2" ht="15">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
     </row>
-    <row r="386" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:2" ht="15">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
     </row>
-    <row r="387" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:2" ht="15">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
     </row>
-    <row r="388" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:2" ht="15">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
     </row>
-    <row r="389" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:2" ht="15">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
     </row>
-    <row r="390" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:2" ht="15">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
     </row>
-    <row r="391" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:2" ht="15">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
     </row>
-    <row r="392" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:2" ht="15">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
     </row>
-    <row r="393" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:2" ht="15">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
     </row>
-    <row r="394" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:2" ht="15">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
     </row>
-    <row r="395" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:2" ht="15">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
     </row>
-    <row r="396" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:2" ht="15">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
     </row>
-    <row r="397" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:2" ht="15">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
     </row>
-    <row r="398" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:2" ht="15">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
     </row>
-    <row r="399" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:2" ht="15">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
     </row>
-    <row r="400" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:2" ht="15">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
     </row>
-    <row r="401" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:2" ht="15">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
     </row>
-    <row r="402" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:2" ht="15">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
     </row>
-    <row r="403" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:2" ht="15">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
     </row>
-    <row r="404" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:2" ht="15">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
     </row>
-    <row r="405" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:2" ht="15">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
     </row>
-    <row r="406" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:2" ht="15">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
     </row>
-    <row r="407" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:2" ht="15">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
     </row>
-    <row r="408" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:2" ht="15">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
     </row>
-    <row r="409" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:2" ht="15">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
     </row>
-    <row r="410" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:2" ht="15">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
     </row>
-    <row r="411" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:2" ht="15">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
     </row>
-    <row r="412" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:2" ht="15">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
     </row>
-    <row r="413" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:2" ht="15">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
     </row>
-    <row r="414" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:2" ht="15">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
     </row>
-    <row r="415" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:2" ht="15">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
     </row>
-    <row r="416" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:2" ht="15">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
     </row>
-    <row r="417" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:2" ht="15">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
     </row>
-    <row r="418" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:2" ht="15">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
     </row>
-    <row r="419" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:2" ht="15">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
     </row>
-    <row r="420" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:2" ht="15">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
     </row>
-    <row r="421" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:2" ht="15">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
     </row>
-    <row r="422" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:2" ht="15">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
     </row>
-    <row r="423" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:2" ht="15">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
     </row>
-    <row r="424" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:2" ht="15">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
     </row>
-    <row r="425" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:2" ht="15">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
     </row>
-    <row r="426" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:2" ht="15">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
     </row>
-    <row r="427" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:2" ht="15">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
     </row>
-    <row r="428" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:2" ht="15">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
     </row>
-    <row r="429" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:2" ht="15">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
     </row>
-    <row r="430" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:2" ht="15">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
     </row>
-    <row r="431" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:2" ht="15">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
     </row>
-    <row r="432" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:2" ht="15">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
     </row>
-    <row r="433" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:2" ht="15">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
     </row>
-    <row r="434" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:2" ht="15">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
     </row>
-    <row r="435" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:2" ht="15">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
     </row>
-    <row r="436" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:2" ht="15">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
     </row>
-    <row r="437" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:2" ht="15">
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
     </row>
-    <row r="438" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:2" ht="15">
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
     </row>
-    <row r="439" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:2" ht="15">
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
     </row>
-    <row r="440" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:2" ht="15">
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
     </row>
-    <row r="441" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:2" ht="15">
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
     </row>
-    <row r="442" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:2" ht="15">
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
     </row>
-    <row r="443" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:2" ht="15">
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
     </row>
-    <row r="444" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:2" ht="15">
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
     </row>
-    <row r="445" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:2" ht="15">
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
     </row>
-    <row r="446" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:2" ht="15">
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
     </row>
-    <row r="447" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:2" ht="15">
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
     </row>
-    <row r="448" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:2" ht="15">
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
     </row>
-    <row r="449" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:2" ht="15">
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
     </row>
-    <row r="450" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:2" ht="15">
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
     </row>
-    <row r="451" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:2" ht="15">
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
     </row>
-    <row r="452" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:2" ht="15">
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
     </row>
-    <row r="453" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:2" ht="15">
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
     </row>
-    <row r="454" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:2" ht="15">
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
     </row>
-    <row r="455" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:2" ht="15">
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
     </row>
-    <row r="456" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:2" ht="15">
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
     </row>
-    <row r="457" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:2" ht="15">
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
     </row>
-    <row r="458" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:2" ht="15">
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
     </row>
-    <row r="459" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:2" ht="15">
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
     </row>
-    <row r="460" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:2" ht="15">
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
     </row>
-    <row r="461" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:2" ht="15">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
     </row>
-    <row r="462" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:2" ht="15">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
     </row>
-    <row r="463" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:2" ht="15">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
     </row>
-    <row r="464" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:2" ht="15">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
     </row>
-    <row r="465" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:2" ht="15">
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
     </row>
-    <row r="466" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:2" ht="15">
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
     </row>
-    <row r="467" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:2" ht="15">
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
     </row>
-    <row r="468" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:2" ht="15">
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
     </row>
-    <row r="469" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:2" ht="15">
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
     </row>
-    <row r="470" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:2" ht="15">
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
     </row>
-    <row r="471" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:2" ht="15">
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
     </row>
-    <row r="472" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:2" ht="15">
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
     </row>
-    <row r="473" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:2" ht="15">
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
     </row>
-    <row r="474" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:2" ht="15">
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
     </row>
-    <row r="475" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:2" ht="15">
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
     </row>
-    <row r="476" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:2" ht="15">
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
     </row>
-    <row r="477" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:2" ht="15">
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
     </row>
-    <row r="478" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:2" ht="15">
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
     </row>
-    <row r="479" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:2" ht="15">
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
     </row>
-    <row r="480" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:2" ht="15">
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
     </row>
-    <row r="481" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:2" ht="15">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
     </row>
-    <row r="482" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:2" ht="15">
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
     </row>
-    <row r="483" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:2" ht="15">
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
     </row>
-    <row r="484" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:2" ht="15">
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
     </row>
-    <row r="485" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:2" ht="15">
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
     </row>
-    <row r="486" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:2" ht="15">
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
     </row>
-    <row r="487" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:2" ht="15">
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
     </row>
-    <row r="488" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:2" ht="15">
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
     </row>
-    <row r="489" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:2" ht="15">
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
     </row>
-    <row r="490" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:2" ht="15">
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
     </row>
-    <row r="491" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:2" ht="15">
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
     </row>
-    <row r="492" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:2" ht="15">
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
     </row>
-    <row r="493" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:2" ht="15">
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
     </row>
-    <row r="494" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:2" ht="15">
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
     </row>
-    <row r="495" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:2" ht="15">
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
     </row>
-    <row r="496" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:2" ht="15">
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
     </row>
-    <row r="497" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:2" ht="15">
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
     </row>
-    <row r="498" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:2" ht="15">
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
     </row>
-    <row r="499" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:2" ht="15">
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
     </row>
-    <row r="500" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:2" ht="15">
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
     </row>
-    <row r="501" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:2" ht="15">
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
     </row>
-    <row r="502" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:2" ht="15">
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
     </row>
-    <row r="503" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:2" ht="15">
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
     </row>
-    <row r="504" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:2" ht="15">
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
     </row>
-    <row r="505" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:2" ht="15">
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
     </row>
-    <row r="506" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:2" ht="15">
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
     </row>
-    <row r="507" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:2" ht="15">
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
     </row>
-    <row r="508" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:2" ht="15">
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
     </row>
-    <row r="509" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:2" ht="15">
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
     </row>
-    <row r="510" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:2" ht="15">
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
     </row>
-    <row r="511" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:2" ht="15">
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
     </row>
-    <row r="512" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:2" ht="15">
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
     </row>
-    <row r="513" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:2" ht="15">
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
     </row>
-    <row r="514" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:2" ht="15">
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
     </row>
-    <row r="515" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:2" ht="15">
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
     </row>
-    <row r="516" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:2" ht="15">
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
     </row>
-    <row r="517" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:2" ht="15">
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
     </row>
-    <row r="518" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:2" ht="15">
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
     </row>
-    <row r="519" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:2" ht="15">
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
     </row>
-    <row r="520" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:2" ht="15">
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
     </row>
-    <row r="521" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:2" ht="15">
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
     </row>
-    <row r="522" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:2" ht="15">
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
     </row>
-    <row r="523" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:2" ht="15">
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
     </row>
-    <row r="524" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:2" ht="15">
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
     </row>
-    <row r="525" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:2" ht="15">
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
     </row>
-    <row r="526" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:2" ht="15">
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
     </row>
-    <row r="527" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:2" ht="15">
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
     </row>
-    <row r="528" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:2" ht="15">
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
     </row>
-    <row r="529" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:2" ht="15">
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
     </row>
-    <row r="530" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:2" ht="15">
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
     </row>
-    <row r="531" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:2" ht="15">
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
     </row>
-    <row r="532" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:2" ht="15">
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
     </row>
-    <row r="533" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:2" ht="15">
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
     </row>
-    <row r="534" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:2" ht="15">
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
     </row>
-    <row r="535" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:2" ht="15">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
     </row>
-    <row r="536" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:2" ht="15">
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
     </row>
-    <row r="537" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:2" ht="15">
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
     </row>
-    <row r="538" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:2" ht="15">
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
     </row>
-    <row r="539" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:2" ht="15">
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
     </row>
-    <row r="540" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:2" ht="15">
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
     </row>
-    <row r="541" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:2" ht="15">
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
     </row>
-    <row r="542" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:2" ht="15">
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
     </row>
-    <row r="543" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:2" ht="15">
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
     </row>

--- a/Treinamento/Planilha Robô Regularizar.xlsx
+++ b/Treinamento/Planilha Robô Regularizar.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28521"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F40FB9A-D947-4365-89C6-ED7A17B828F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="268" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{804B0DE8-F9C7-4C8D-BDB4-3D47F4989FE1}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="-120" windowWidth="19530" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
+    <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="4">
   <si>
     <t>Recibo</t>
   </si>
@@ -54,7 +54,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -72,6 +72,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -123,11 +129,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -147,7 +157,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -443,14 +453,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDA9D80-CE6D-4C1A-B019-EB3A00964886}">
-  <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B543"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -458,261 +468,1902 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2">
-        <v>526987932</v>
-      </c>
-      <c r="B2" t="s">
+        <v>747600330</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3">
-        <v>747937278</v>
-      </c>
-      <c r="B3" t="s">
+        <v>646707673</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4">
-        <v>740990647</v>
-      </c>
-      <c r="B4" t="s">
+        <v>732809540</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5">
-        <v>740144625</v>
-      </c>
-      <c r="B5" t="s">
+        <v>737499289</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6">
-        <v>726591062</v>
-      </c>
-      <c r="B6" t="s">
+        <v>737492268</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7">
-        <v>734143823</v>
-      </c>
-      <c r="B7" t="s">
+        <v>736673637</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8">
-        <v>731510339</v>
-      </c>
-      <c r="B8" t="s">
+        <v>726732708</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9">
-        <v>679868541</v>
-      </c>
-      <c r="B9" t="s">
+        <v>726732690</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10">
-        <v>633240753</v>
-      </c>
-      <c r="B10" t="s">
+        <v>677566980</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11">
-        <v>664451907</v>
-      </c>
-      <c r="B11" t="s">
+        <v>675809887</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12">
-        <v>666424449</v>
-      </c>
-      <c r="B12" t="s">
+        <v>668998572</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13">
-        <v>656758608</v>
-      </c>
-      <c r="B13" t="s">
+        <v>657358168</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14">
-        <v>657608505</v>
-      </c>
-      <c r="B14" t="s">
+        <v>649321928</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15">
-        <v>627250578</v>
-      </c>
-      <c r="B15" t="s">
+        <v>611821624</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16">
-        <v>595260021</v>
-      </c>
-      <c r="B16" t="s">
+        <v>630952913</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17">
-        <v>616970533</v>
-      </c>
-      <c r="B17" t="s">
+        <v>632987842</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18">
-        <v>612388078</v>
-      </c>
-      <c r="B18" t="s">
+        <v>627209343</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19">
-        <v>610612115</v>
-      </c>
-      <c r="B19" t="s">
+        <v>625605955</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20">
-        <v>600080844</v>
-      </c>
-      <c r="B20" t="s">
+        <v>608909929</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21">
-        <v>599800814</v>
-      </c>
-      <c r="B21" t="s">
+        <v>605216187</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22">
-        <v>591918218</v>
-      </c>
-      <c r="B22" t="s">
+        <v>602168936</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23">
-        <v>580611295</v>
-      </c>
-      <c r="B23" t="s">
+        <v>597430473</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24">
-        <v>579980016</v>
-      </c>
-      <c r="B24" t="s">
+        <v>596170047</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2">
       <c r="A25">
-        <v>172884854</v>
-      </c>
-      <c r="B25" t="s">
+        <v>591222512</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26">
-        <v>171363942</v>
-      </c>
-      <c r="B26" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+        <v>563921323</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
-        <v>711727143</v>
-      </c>
-      <c r="B27" t="s">
+        <v>746220874</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2">
       <c r="A28">
-        <v>717158475</v>
-      </c>
-      <c r="B28" t="s">
+        <v>740615491</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2">
       <c r="A29">
-        <v>620694335</v>
-      </c>
-      <c r="B29" t="s">
+        <v>671502478</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2">
       <c r="A30">
-        <v>634307957</v>
-      </c>
-      <c r="B30" t="s">
+        <v>714434507</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2">
       <c r="A31">
-        <v>665950485</v>
-      </c>
-      <c r="B31" t="s">
+        <v>738338270</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2">
       <c r="A32">
-        <v>667547461</v>
-      </c>
-      <c r="B32" t="s">
+        <v>701009239</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33">
-        <v>661083216</v>
-      </c>
-      <c r="B33" t="s">
+        <v>686508759</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>677239968</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>620056790</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>634008068</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>630242968</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="B38" s="4"/>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="B39" s="4"/>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="B40" s="4"/>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="B41" s="4"/>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="B42" s="4"/>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="B43" s="4"/>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="B44" s="4"/>
+    </row>
+    <row r="147" spans="1:2" ht="15">
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+    </row>
+    <row r="148" spans="1:2" ht="15">
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
+    </row>
+    <row r="149" spans="1:2" ht="15">
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+    </row>
+    <row r="150" spans="1:2" ht="15">
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+    </row>
+    <row r="151" spans="1:2" ht="15">
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+    </row>
+    <row r="152" spans="1:2" ht="15">
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
+    </row>
+    <row r="153" spans="1:2" ht="15">
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+    </row>
+    <row r="154" spans="1:2" ht="15">
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+    </row>
+    <row r="155" spans="1:2" ht="15">
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+    </row>
+    <row r="156" spans="1:2" ht="15">
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
+    </row>
+    <row r="157" spans="1:2" ht="15">
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+    </row>
+    <row r="158" spans="1:2" ht="15">
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
+    </row>
+    <row r="159" spans="1:2" ht="15">
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+    </row>
+    <row r="160" spans="1:2" ht="15">
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
+    </row>
+    <row r="161" spans="1:2" ht="15">
+      <c r="A161" s="3"/>
+      <c r="B161" s="3"/>
+    </row>
+    <row r="162" spans="1:2" ht="15">
+      <c r="A162" s="3"/>
+      <c r="B162" s="3"/>
+    </row>
+    <row r="163" spans="1:2" ht="15">
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
+    </row>
+    <row r="164" spans="1:2" ht="15">
+      <c r="A164" s="3"/>
+      <c r="B164" s="3"/>
+    </row>
+    <row r="165" spans="1:2" ht="15">
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+    </row>
+    <row r="166" spans="1:2" ht="15">
+      <c r="A166" s="3"/>
+      <c r="B166" s="3"/>
+    </row>
+    <row r="167" spans="1:2" ht="15">
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
+    </row>
+    <row r="168" spans="1:2" ht="15">
+      <c r="A168" s="3"/>
+      <c r="B168" s="3"/>
+    </row>
+    <row r="169" spans="1:2" ht="15">
+      <c r="A169" s="3"/>
+      <c r="B169" s="3"/>
+    </row>
+    <row r="170" spans="1:2" ht="15">
+      <c r="A170" s="3"/>
+      <c r="B170" s="3"/>
+    </row>
+    <row r="171" spans="1:2" ht="15">
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
+    </row>
+    <row r="172" spans="1:2" ht="15">
+      <c r="A172" s="3"/>
+      <c r="B172" s="3"/>
+    </row>
+    <row r="173" spans="1:2" ht="15">
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
+    </row>
+    <row r="174" spans="1:2" ht="15">
+      <c r="A174" s="3"/>
+      <c r="B174" s="3"/>
+    </row>
+    <row r="175" spans="1:2" ht="15">
+      <c r="A175" s="3"/>
+      <c r="B175" s="3"/>
+    </row>
+    <row r="176" spans="1:2" ht="15">
+      <c r="A176" s="3"/>
+      <c r="B176" s="3"/>
+    </row>
+    <row r="177" spans="1:2" ht="15">
+      <c r="A177" s="3"/>
+      <c r="B177" s="3"/>
+    </row>
+    <row r="178" spans="1:2" ht="15">
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
+    </row>
+    <row r="179" spans="1:2" ht="15">
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
+    </row>
+    <row r="180" spans="1:2" ht="15">
+      <c r="A180" s="3"/>
+      <c r="B180" s="3"/>
+    </row>
+    <row r="181" spans="1:2" ht="15">
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
+    </row>
+    <row r="182" spans="1:2" ht="15">
+      <c r="A182" s="3"/>
+      <c r="B182" s="3"/>
+    </row>
+    <row r="183" spans="1:2" ht="15">
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
+    </row>
+    <row r="184" spans="1:2" ht="15">
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
+    </row>
+    <row r="185" spans="1:2" ht="15">
+      <c r="A185" s="3"/>
+      <c r="B185" s="3"/>
+    </row>
+    <row r="186" spans="1:2" ht="15">
+      <c r="A186" s="3"/>
+      <c r="B186" s="3"/>
+    </row>
+    <row r="187" spans="1:2" ht="15">
+      <c r="A187" s="3"/>
+      <c r="B187" s="3"/>
+    </row>
+    <row r="188" spans="1:2" ht="15">
+      <c r="A188" s="3"/>
+      <c r="B188" s="3"/>
+    </row>
+    <row r="189" spans="1:2" ht="15">
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
+    </row>
+    <row r="190" spans="1:2" ht="15">
+      <c r="A190" s="3"/>
+      <c r="B190" s="3"/>
+    </row>
+    <row r="191" spans="1:2" ht="15">
+      <c r="A191" s="3"/>
+      <c r="B191" s="3"/>
+    </row>
+    <row r="192" spans="1:2" ht="15">
+      <c r="A192" s="3"/>
+      <c r="B192" s="3"/>
+    </row>
+    <row r="193" spans="1:2" ht="15">
+      <c r="A193" s="3"/>
+      <c r="B193" s="3"/>
+    </row>
+    <row r="194" spans="1:2" ht="15">
+      <c r="A194" s="3"/>
+      <c r="B194" s="3"/>
+    </row>
+    <row r="195" spans="1:2" ht="15">
+      <c r="A195" s="3"/>
+      <c r="B195" s="3"/>
+    </row>
+    <row r="196" spans="1:2" ht="15">
+      <c r="A196" s="3"/>
+      <c r="B196" s="3"/>
+    </row>
+    <row r="197" spans="1:2" ht="15">
+      <c r="A197" s="3"/>
+      <c r="B197" s="3"/>
+    </row>
+    <row r="198" spans="1:2" ht="15">
+      <c r="A198" s="3"/>
+      <c r="B198" s="3"/>
+    </row>
+    <row r="199" spans="1:2" ht="15">
+      <c r="A199" s="3"/>
+      <c r="B199" s="3"/>
+    </row>
+    <row r="200" spans="1:2" ht="15">
+      <c r="A200" s="3"/>
+      <c r="B200" s="3"/>
+    </row>
+    <row r="201" spans="1:2" ht="15">
+      <c r="A201" s="3"/>
+      <c r="B201" s="3"/>
+    </row>
+    <row r="202" spans="1:2" ht="15">
+      <c r="A202" s="3"/>
+      <c r="B202" s="3"/>
+    </row>
+    <row r="203" spans="1:2" ht="15">
+      <c r="A203" s="3"/>
+      <c r="B203" s="3"/>
+    </row>
+    <row r="204" spans="1:2" ht="15">
+      <c r="A204" s="3"/>
+      <c r="B204" s="3"/>
+    </row>
+    <row r="205" spans="1:2" ht="15">
+      <c r="A205" s="3"/>
+      <c r="B205" s="3"/>
+    </row>
+    <row r="206" spans="1:2" ht="15">
+      <c r="A206" s="3"/>
+      <c r="B206" s="3"/>
+    </row>
+    <row r="207" spans="1:2" ht="15">
+      <c r="A207" s="3"/>
+      <c r="B207" s="3"/>
+    </row>
+    <row r="208" spans="1:2" ht="15">
+      <c r="A208" s="3"/>
+      <c r="B208" s="3"/>
+    </row>
+    <row r="209" spans="1:2" ht="15">
+      <c r="A209" s="3"/>
+      <c r="B209" s="3"/>
+    </row>
+    <row r="210" spans="1:2" ht="15">
+      <c r="A210" s="3"/>
+      <c r="B210" s="3"/>
+    </row>
+    <row r="211" spans="1:2" ht="15">
+      <c r="A211" s="3"/>
+      <c r="B211" s="3"/>
+    </row>
+    <row r="212" spans="1:2" ht="15">
+      <c r="A212" s="3"/>
+      <c r="B212" s="3"/>
+    </row>
+    <row r="213" spans="1:2" ht="15">
+      <c r="A213" s="3"/>
+      <c r="B213" s="3"/>
+    </row>
+    <row r="214" spans="1:2" ht="15">
+      <c r="A214" s="3"/>
+      <c r="B214" s="3"/>
+    </row>
+    <row r="215" spans="1:2" ht="15">
+      <c r="A215" s="3"/>
+      <c r="B215" s="3"/>
+    </row>
+    <row r="216" spans="1:2" ht="15">
+      <c r="A216" s="3"/>
+      <c r="B216" s="3"/>
+    </row>
+    <row r="217" spans="1:2" ht="15">
+      <c r="A217" s="3"/>
+      <c r="B217" s="3"/>
+    </row>
+    <row r="218" spans="1:2" ht="15">
+      <c r="A218" s="3"/>
+      <c r="B218" s="3"/>
+    </row>
+    <row r="219" spans="1:2" ht="15">
+      <c r="A219" s="3"/>
+      <c r="B219" s="3"/>
+    </row>
+    <row r="220" spans="1:2" ht="15">
+      <c r="A220" s="3"/>
+      <c r="B220" s="3"/>
+    </row>
+    <row r="221" spans="1:2" ht="15">
+      <c r="A221" s="3"/>
+      <c r="B221" s="3"/>
+    </row>
+    <row r="222" spans="1:2" ht="15">
+      <c r="A222" s="3"/>
+      <c r="B222" s="3"/>
+    </row>
+    <row r="223" spans="1:2" ht="15">
+      <c r="A223" s="3"/>
+      <c r="B223" s="3"/>
+    </row>
+    <row r="224" spans="1:2" ht="15">
+      <c r="A224" s="3"/>
+      <c r="B224" s="3"/>
+    </row>
+    <row r="225" spans="1:2" ht="15">
+      <c r="A225" s="3"/>
+      <c r="B225" s="3"/>
+    </row>
+    <row r="226" spans="1:2" ht="15">
+      <c r="A226" s="3"/>
+      <c r="B226" s="3"/>
+    </row>
+    <row r="227" spans="1:2" ht="15">
+      <c r="A227" s="3"/>
+      <c r="B227" s="3"/>
+    </row>
+    <row r="228" spans="1:2" ht="15">
+      <c r="A228" s="3"/>
+      <c r="B228" s="3"/>
+    </row>
+    <row r="229" spans="1:2" ht="15">
+      <c r="A229" s="3"/>
+      <c r="B229" s="3"/>
+    </row>
+    <row r="230" spans="1:2" ht="15">
+      <c r="A230" s="3"/>
+      <c r="B230" s="3"/>
+    </row>
+    <row r="231" spans="1:2" ht="15">
+      <c r="A231" s="3"/>
+      <c r="B231" s="3"/>
+    </row>
+    <row r="232" spans="1:2" ht="15">
+      <c r="A232" s="3"/>
+      <c r="B232" s="3"/>
+    </row>
+    <row r="233" spans="1:2" ht="15">
+      <c r="A233" s="3"/>
+      <c r="B233" s="3"/>
+    </row>
+    <row r="234" spans="1:2" ht="15">
+      <c r="A234" s="3"/>
+      <c r="B234" s="3"/>
+    </row>
+    <row r="235" spans="1:2" ht="15">
+      <c r="A235" s="3"/>
+      <c r="B235" s="3"/>
+    </row>
+    <row r="236" spans="1:2" ht="15">
+      <c r="A236" s="3"/>
+      <c r="B236" s="3"/>
+    </row>
+    <row r="237" spans="1:2" ht="15">
+      <c r="A237" s="3"/>
+      <c r="B237" s="3"/>
+    </row>
+    <row r="238" spans="1:2" ht="15">
+      <c r="A238" s="3"/>
+      <c r="B238" s="3"/>
+    </row>
+    <row r="239" spans="1:2" ht="15">
+      <c r="A239" s="3"/>
+      <c r="B239" s="3"/>
+    </row>
+    <row r="240" spans="1:2" ht="15">
+      <c r="A240" s="3"/>
+      <c r="B240" s="3"/>
+    </row>
+    <row r="241" spans="1:2" ht="15">
+      <c r="A241" s="3"/>
+      <c r="B241" s="3"/>
+    </row>
+    <row r="242" spans="1:2" ht="15">
+      <c r="A242" s="3"/>
+      <c r="B242" s="3"/>
+    </row>
+    <row r="243" spans="1:2" ht="15">
+      <c r="A243" s="3"/>
+      <c r="B243" s="3"/>
+    </row>
+    <row r="244" spans="1:2" ht="15">
+      <c r="A244" s="3"/>
+      <c r="B244" s="3"/>
+    </row>
+    <row r="245" spans="1:2" ht="15">
+      <c r="A245" s="3"/>
+      <c r="B245" s="3"/>
+    </row>
+    <row r="246" spans="1:2" ht="15">
+      <c r="A246" s="3"/>
+      <c r="B246" s="3"/>
+    </row>
+    <row r="247" spans="1:2" ht="15">
+      <c r="A247" s="3"/>
+      <c r="B247" s="3"/>
+    </row>
+    <row r="248" spans="1:2" ht="15">
+      <c r="A248" s="3"/>
+      <c r="B248" s="3"/>
+    </row>
+    <row r="249" spans="1:2" ht="15">
+      <c r="A249" s="3"/>
+      <c r="B249" s="3"/>
+    </row>
+    <row r="250" spans="1:2" ht="15">
+      <c r="A250" s="3"/>
+      <c r="B250" s="3"/>
+    </row>
+    <row r="251" spans="1:2" ht="15">
+      <c r="A251" s="3"/>
+      <c r="B251" s="3"/>
+    </row>
+    <row r="252" spans="1:2" ht="15">
+      <c r="A252" s="3"/>
+      <c r="B252" s="3"/>
+    </row>
+    <row r="253" spans="1:2" ht="15">
+      <c r="A253" s="3"/>
+      <c r="B253" s="3"/>
+    </row>
+    <row r="254" spans="1:2" ht="15">
+      <c r="A254" s="3"/>
+      <c r="B254" s="3"/>
+    </row>
+    <row r="255" spans="1:2" ht="15">
+      <c r="A255" s="3"/>
+      <c r="B255" s="3"/>
+    </row>
+    <row r="256" spans="1:2" ht="15">
+      <c r="A256" s="3"/>
+      <c r="B256" s="3"/>
+    </row>
+    <row r="257" spans="1:2" ht="15">
+      <c r="A257" s="3"/>
+      <c r="B257" s="3"/>
+    </row>
+    <row r="258" spans="1:2" ht="15">
+      <c r="A258" s="3"/>
+      <c r="B258" s="3"/>
+    </row>
+    <row r="259" spans="1:2" ht="15">
+      <c r="A259" s="3"/>
+      <c r="B259" s="3"/>
+    </row>
+    <row r="260" spans="1:2" ht="15">
+      <c r="A260" s="3"/>
+      <c r="B260" s="3"/>
+    </row>
+    <row r="261" spans="1:2" ht="15">
+      <c r="A261" s="3"/>
+      <c r="B261" s="3"/>
+    </row>
+    <row r="262" spans="1:2" ht="15">
+      <c r="A262" s="3"/>
+      <c r="B262" s="3"/>
+    </row>
+    <row r="263" spans="1:2" ht="15">
+      <c r="A263" s="3"/>
+      <c r="B263" s="3"/>
+    </row>
+    <row r="264" spans="1:2" ht="15">
+      <c r="A264" s="3"/>
+      <c r="B264" s="3"/>
+    </row>
+    <row r="265" spans="1:2" ht="15">
+      <c r="A265" s="3"/>
+      <c r="B265" s="3"/>
+    </row>
+    <row r="266" spans="1:2" ht="15">
+      <c r="A266" s="3"/>
+      <c r="B266" s="3"/>
+    </row>
+    <row r="267" spans="1:2" ht="15">
+      <c r="A267" s="3"/>
+      <c r="B267" s="3"/>
+    </row>
+    <row r="268" spans="1:2" ht="15">
+      <c r="A268" s="3"/>
+      <c r="B268" s="3"/>
+    </row>
+    <row r="269" spans="1:2" ht="15">
+      <c r="A269" s="3"/>
+      <c r="B269" s="3"/>
+    </row>
+    <row r="270" spans="1:2" ht="15">
+      <c r="A270" s="3"/>
+      <c r="B270" s="3"/>
+    </row>
+    <row r="271" spans="1:2" ht="15">
+      <c r="A271" s="3"/>
+      <c r="B271" s="3"/>
+    </row>
+    <row r="272" spans="1:2" ht="15">
+      <c r="A272" s="3"/>
+      <c r="B272" s="3"/>
+    </row>
+    <row r="273" spans="1:2" ht="15">
+      <c r="A273" s="3"/>
+      <c r="B273" s="3"/>
+    </row>
+    <row r="274" spans="1:2" ht="15">
+      <c r="A274" s="3"/>
+      <c r="B274" s="3"/>
+    </row>
+    <row r="275" spans="1:2" ht="15">
+      <c r="A275" s="3"/>
+      <c r="B275" s="3"/>
+    </row>
+    <row r="276" spans="1:2" ht="15">
+      <c r="A276" s="3"/>
+      <c r="B276" s="3"/>
+    </row>
+    <row r="277" spans="1:2" ht="15">
+      <c r="A277" s="3"/>
+      <c r="B277" s="3"/>
+    </row>
+    <row r="278" spans="1:2" ht="15">
+      <c r="A278" s="3"/>
+      <c r="B278" s="3"/>
+    </row>
+    <row r="279" spans="1:2" ht="15">
+      <c r="A279" s="3"/>
+      <c r="B279" s="3"/>
+    </row>
+    <row r="280" spans="1:2" ht="15">
+      <c r="A280" s="3"/>
+      <c r="B280" s="3"/>
+    </row>
+    <row r="281" spans="1:2" ht="15">
+      <c r="A281" s="3"/>
+      <c r="B281" s="3"/>
+    </row>
+    <row r="282" spans="1:2" ht="15">
+      <c r="A282" s="3"/>
+      <c r="B282" s="3"/>
+    </row>
+    <row r="283" spans="1:2" ht="15">
+      <c r="A283" s="3"/>
+      <c r="B283" s="3"/>
+    </row>
+    <row r="284" spans="1:2" ht="15">
+      <c r="A284" s="3"/>
+      <c r="B284" s="3"/>
+    </row>
+    <row r="285" spans="1:2" ht="15">
+      <c r="A285" s="3"/>
+      <c r="B285" s="3"/>
+    </row>
+    <row r="286" spans="1:2" ht="15">
+      <c r="A286" s="3"/>
+      <c r="B286" s="3"/>
+    </row>
+    <row r="287" spans="1:2" ht="15">
+      <c r="A287" s="3"/>
+      <c r="B287" s="3"/>
+    </row>
+    <row r="288" spans="1:2" ht="15">
+      <c r="A288" s="3"/>
+      <c r="B288" s="3"/>
+    </row>
+    <row r="289" spans="1:2" ht="15">
+      <c r="A289" s="3"/>
+      <c r="B289" s="3"/>
+    </row>
+    <row r="290" spans="1:2" ht="15">
+      <c r="A290" s="3"/>
+      <c r="B290" s="3"/>
+    </row>
+    <row r="291" spans="1:2" ht="15">
+      <c r="A291" s="3"/>
+      <c r="B291" s="3"/>
+    </row>
+    <row r="292" spans="1:2" ht="15">
+      <c r="A292" s="3"/>
+      <c r="B292" s="3"/>
+    </row>
+    <row r="293" spans="1:2" ht="15">
+      <c r="A293" s="3"/>
+      <c r="B293" s="3"/>
+    </row>
+    <row r="294" spans="1:2" ht="15">
+      <c r="A294" s="3"/>
+      <c r="B294" s="3"/>
+    </row>
+    <row r="295" spans="1:2" ht="15">
+      <c r="A295" s="3"/>
+      <c r="B295" s="3"/>
+    </row>
+    <row r="296" spans="1:2" ht="15">
+      <c r="A296" s="3"/>
+      <c r="B296" s="3"/>
+    </row>
+    <row r="297" spans="1:2" ht="15">
+      <c r="A297" s="3"/>
+      <c r="B297" s="3"/>
+    </row>
+    <row r="298" spans="1:2" ht="15">
+      <c r="A298" s="3"/>
+      <c r="B298" s="3"/>
+    </row>
+    <row r="299" spans="1:2" ht="15">
+      <c r="A299" s="3"/>
+      <c r="B299" s="3"/>
+    </row>
+    <row r="300" spans="1:2" ht="15">
+      <c r="A300" s="3"/>
+      <c r="B300" s="3"/>
+    </row>
+    <row r="301" spans="1:2" ht="15">
+      <c r="A301" s="3"/>
+      <c r="B301" s="3"/>
+    </row>
+    <row r="302" spans="1:2" ht="15">
+      <c r="A302" s="3"/>
+      <c r="B302" s="3"/>
+    </row>
+    <row r="303" spans="1:2" ht="15">
+      <c r="A303" s="3"/>
+      <c r="B303" s="3"/>
+    </row>
+    <row r="304" spans="1:2" ht="15">
+      <c r="A304" s="3"/>
+      <c r="B304" s="3"/>
+    </row>
+    <row r="305" spans="1:2" ht="15">
+      <c r="A305" s="3"/>
+      <c r="B305" s="3"/>
+    </row>
+    <row r="306" spans="1:2" ht="15">
+      <c r="A306" s="3"/>
+      <c r="B306" s="3"/>
+    </row>
+    <row r="307" spans="1:2" ht="15">
+      <c r="A307" s="3"/>
+      <c r="B307" s="3"/>
+    </row>
+    <row r="308" spans="1:2" ht="15">
+      <c r="A308" s="3"/>
+      <c r="B308" s="3"/>
+    </row>
+    <row r="309" spans="1:2" ht="15">
+      <c r="A309" s="3"/>
+      <c r="B309" s="3"/>
+    </row>
+    <row r="310" spans="1:2" ht="15">
+      <c r="A310" s="3"/>
+      <c r="B310" s="3"/>
+    </row>
+    <row r="311" spans="1:2" ht="15">
+      <c r="A311" s="3"/>
+      <c r="B311" s="3"/>
+    </row>
+    <row r="312" spans="1:2" ht="15">
+      <c r="A312" s="3"/>
+      <c r="B312" s="3"/>
+    </row>
+    <row r="313" spans="1:2" ht="15">
+      <c r="A313" s="3"/>
+      <c r="B313" s="3"/>
+    </row>
+    <row r="314" spans="1:2" ht="15">
+      <c r="A314" s="3"/>
+      <c r="B314" s="3"/>
+    </row>
+    <row r="315" spans="1:2" ht="15">
+      <c r="A315" s="3"/>
+      <c r="B315" s="3"/>
+    </row>
+    <row r="316" spans="1:2" ht="15">
+      <c r="A316" s="3"/>
+      <c r="B316" s="3"/>
+    </row>
+    <row r="317" spans="1:2" ht="15">
+      <c r="A317" s="3"/>
+      <c r="B317" s="3"/>
+    </row>
+    <row r="318" spans="1:2" ht="15">
+      <c r="A318" s="3"/>
+      <c r="B318" s="3"/>
+    </row>
+    <row r="319" spans="1:2" ht="15">
+      <c r="A319" s="3"/>
+      <c r="B319" s="3"/>
+    </row>
+    <row r="320" spans="1:2" ht="15">
+      <c r="A320" s="3"/>
+      <c r="B320" s="3"/>
+    </row>
+    <row r="321" spans="1:2" ht="15">
+      <c r="A321" s="3"/>
+      <c r="B321" s="3"/>
+    </row>
+    <row r="322" spans="1:2" ht="15">
+      <c r="A322" s="3"/>
+      <c r="B322" s="3"/>
+    </row>
+    <row r="323" spans="1:2" ht="15">
+      <c r="A323" s="3"/>
+      <c r="B323" s="3"/>
+    </row>
+    <row r="324" spans="1:2" ht="15">
+      <c r="A324" s="3"/>
+      <c r="B324" s="3"/>
+    </row>
+    <row r="325" spans="1:2" ht="15">
+      <c r="A325" s="3"/>
+      <c r="B325" s="3"/>
+    </row>
+    <row r="326" spans="1:2" ht="15">
+      <c r="A326" s="3"/>
+      <c r="B326" s="3"/>
+    </row>
+    <row r="327" spans="1:2" ht="15">
+      <c r="A327" s="3"/>
+      <c r="B327" s="3"/>
+    </row>
+    <row r="328" spans="1:2" ht="15">
+      <c r="A328" s="3"/>
+      <c r="B328" s="3"/>
+    </row>
+    <row r="329" spans="1:2" ht="15">
+      <c r="A329" s="3"/>
+      <c r="B329" s="3"/>
+    </row>
+    <row r="330" spans="1:2" ht="15">
+      <c r="A330" s="3"/>
+      <c r="B330" s="3"/>
+    </row>
+    <row r="331" spans="1:2" ht="15">
+      <c r="A331" s="3"/>
+      <c r="B331" s="3"/>
+    </row>
+    <row r="332" spans="1:2" ht="15">
+      <c r="A332" s="3"/>
+      <c r="B332" s="3"/>
+    </row>
+    <row r="333" spans="1:2" ht="15">
+      <c r="A333" s="3"/>
+      <c r="B333" s="3"/>
+    </row>
+    <row r="334" spans="1:2" ht="15">
+      <c r="A334" s="3"/>
+      <c r="B334" s="3"/>
+    </row>
+    <row r="335" spans="1:2" ht="15">
+      <c r="A335" s="3"/>
+      <c r="B335" s="3"/>
+    </row>
+    <row r="336" spans="1:2" ht="15">
+      <c r="A336" s="3"/>
+      <c r="B336" s="3"/>
+    </row>
+    <row r="337" spans="1:2" ht="15">
+      <c r="A337" s="3"/>
+      <c r="B337" s="3"/>
+    </row>
+    <row r="338" spans="1:2" ht="15">
+      <c r="A338" s="3"/>
+      <c r="B338" s="3"/>
+    </row>
+    <row r="339" spans="1:2" ht="15">
+      <c r="A339" s="3"/>
+      <c r="B339" s="3"/>
+    </row>
+    <row r="340" spans="1:2" ht="15">
+      <c r="A340" s="3"/>
+      <c r="B340" s="3"/>
+    </row>
+    <row r="341" spans="1:2" ht="15">
+      <c r="A341" s="3"/>
+      <c r="B341" s="3"/>
+    </row>
+    <row r="342" spans="1:2" ht="15">
+      <c r="A342" s="3"/>
+      <c r="B342" s="3"/>
+    </row>
+    <row r="343" spans="1:2" ht="15">
+      <c r="A343" s="3"/>
+      <c r="B343" s="3"/>
+    </row>
+    <row r="344" spans="1:2" ht="15">
+      <c r="A344" s="3"/>
+      <c r="B344" s="3"/>
+    </row>
+    <row r="345" spans="1:2" ht="15">
+      <c r="A345" s="3"/>
+      <c r="B345" s="3"/>
+    </row>
+    <row r="346" spans="1:2" ht="15">
+      <c r="A346" s="3"/>
+      <c r="B346" s="3"/>
+    </row>
+    <row r="347" spans="1:2" ht="15">
+      <c r="A347" s="3"/>
+      <c r="B347" s="3"/>
+    </row>
+    <row r="348" spans="1:2" ht="15">
+      <c r="A348" s="3"/>
+      <c r="B348" s="3"/>
+    </row>
+    <row r="349" spans="1:2" ht="15">
+      <c r="A349" s="3"/>
+      <c r="B349" s="3"/>
+    </row>
+    <row r="350" spans="1:2" ht="15">
+      <c r="A350" s="3"/>
+      <c r="B350" s="3"/>
+    </row>
+    <row r="351" spans="1:2" ht="15">
+      <c r="A351" s="3"/>
+      <c r="B351" s="3"/>
+    </row>
+    <row r="352" spans="1:2" ht="15">
+      <c r="A352" s="3"/>
+      <c r="B352" s="3"/>
+    </row>
+    <row r="353" spans="1:2" ht="15">
+      <c r="A353" s="3"/>
+      <c r="B353" s="3"/>
+    </row>
+    <row r="354" spans="1:2" ht="15">
+      <c r="A354" s="3"/>
+      <c r="B354" s="3"/>
+    </row>
+    <row r="355" spans="1:2" ht="15">
+      <c r="A355" s="3"/>
+      <c r="B355" s="3"/>
+    </row>
+    <row r="356" spans="1:2" ht="15">
+      <c r="A356" s="3"/>
+      <c r="B356" s="3"/>
+    </row>
+    <row r="357" spans="1:2" ht="15">
+      <c r="A357" s="3"/>
+      <c r="B357" s="3"/>
+    </row>
+    <row r="358" spans="1:2" ht="15">
+      <c r="A358" s="3"/>
+      <c r="B358" s="3"/>
+    </row>
+    <row r="359" spans="1:2" ht="15">
+      <c r="A359" s="3"/>
+      <c r="B359" s="3"/>
+    </row>
+    <row r="360" spans="1:2" ht="15">
+      <c r="A360" s="3"/>
+      <c r="B360" s="3"/>
+    </row>
+    <row r="361" spans="1:2" ht="15">
+      <c r="A361" s="3"/>
+      <c r="B361" s="3"/>
+    </row>
+    <row r="362" spans="1:2" ht="15">
+      <c r="A362" s="3"/>
+      <c r="B362" s="3"/>
+    </row>
+    <row r="363" spans="1:2" ht="15">
+      <c r="A363" s="3"/>
+      <c r="B363" s="3"/>
+    </row>
+    <row r="364" spans="1:2" ht="15">
+      <c r="A364" s="3"/>
+      <c r="B364" s="3"/>
+    </row>
+    <row r="365" spans="1:2" ht="15">
+      <c r="A365" s="3"/>
+      <c r="B365" s="3"/>
+    </row>
+    <row r="366" spans="1:2" ht="15">
+      <c r="A366" s="3"/>
+      <c r="B366" s="3"/>
+    </row>
+    <row r="367" spans="1:2" ht="15">
+      <c r="A367" s="3"/>
+      <c r="B367" s="3"/>
+    </row>
+    <row r="368" spans="1:2" ht="15">
+      <c r="A368" s="3"/>
+      <c r="B368" s="3"/>
+    </row>
+    <row r="369" spans="1:2" ht="15">
+      <c r="A369" s="3"/>
+      <c r="B369" s="3"/>
+    </row>
+    <row r="370" spans="1:2" ht="15">
+      <c r="A370" s="3"/>
+      <c r="B370" s="3"/>
+    </row>
+    <row r="371" spans="1:2" ht="15">
+      <c r="A371" s="3"/>
+      <c r="B371" s="3"/>
+    </row>
+    <row r="372" spans="1:2" ht="15">
+      <c r="A372" s="3"/>
+      <c r="B372" s="3"/>
+    </row>
+    <row r="373" spans="1:2" ht="15">
+      <c r="A373" s="3"/>
+      <c r="B373" s="3"/>
+    </row>
+    <row r="374" spans="1:2" ht="15">
+      <c r="A374" s="3"/>
+      <c r="B374" s="3"/>
+    </row>
+    <row r="375" spans="1:2" ht="15">
+      <c r="A375" s="3"/>
+      <c r="B375" s="3"/>
+    </row>
+    <row r="376" spans="1:2" ht="15">
+      <c r="A376" s="3"/>
+      <c r="B376" s="3"/>
+    </row>
+    <row r="377" spans="1:2" ht="15">
+      <c r="A377" s="3"/>
+      <c r="B377" s="3"/>
+    </row>
+    <row r="378" spans="1:2" ht="15">
+      <c r="A378" s="3"/>
+      <c r="B378" s="3"/>
+    </row>
+    <row r="379" spans="1:2" ht="15">
+      <c r="A379" s="3"/>
+      <c r="B379" s="3"/>
+    </row>
+    <row r="380" spans="1:2" ht="15">
+      <c r="A380" s="3"/>
+      <c r="B380" s="3"/>
+    </row>
+    <row r="381" spans="1:2" ht="15">
+      <c r="A381" s="3"/>
+      <c r="B381" s="3"/>
+    </row>
+    <row r="382" spans="1:2" ht="15">
+      <c r="A382" s="3"/>
+      <c r="B382" s="3"/>
+    </row>
+    <row r="383" spans="1:2" ht="15">
+      <c r="A383" s="3"/>
+      <c r="B383" s="3"/>
+    </row>
+    <row r="384" spans="1:2" ht="15">
+      <c r="A384" s="3"/>
+      <c r="B384" s="3"/>
+    </row>
+    <row r="385" spans="1:2" ht="15">
+      <c r="A385" s="3"/>
+      <c r="B385" s="3"/>
+    </row>
+    <row r="386" spans="1:2" ht="15">
+      <c r="A386" s="3"/>
+      <c r="B386" s="3"/>
+    </row>
+    <row r="387" spans="1:2" ht="15">
+      <c r="A387" s="3"/>
+      <c r="B387" s="3"/>
+    </row>
+    <row r="388" spans="1:2" ht="15">
+      <c r="A388" s="3"/>
+      <c r="B388" s="3"/>
+    </row>
+    <row r="389" spans="1:2" ht="15">
+      <c r="A389" s="3"/>
+      <c r="B389" s="3"/>
+    </row>
+    <row r="390" spans="1:2" ht="15">
+      <c r="A390" s="3"/>
+      <c r="B390" s="3"/>
+    </row>
+    <row r="391" spans="1:2" ht="15">
+      <c r="A391" s="3"/>
+      <c r="B391" s="3"/>
+    </row>
+    <row r="392" spans="1:2" ht="15">
+      <c r="A392" s="3"/>
+      <c r="B392" s="3"/>
+    </row>
+    <row r="393" spans="1:2" ht="15">
+      <c r="A393" s="3"/>
+      <c r="B393" s="3"/>
+    </row>
+    <row r="394" spans="1:2" ht="15">
+      <c r="A394" s="3"/>
+      <c r="B394" s="3"/>
+    </row>
+    <row r="395" spans="1:2" ht="15">
+      <c r="A395" s="3"/>
+      <c r="B395" s="3"/>
+    </row>
+    <row r="396" spans="1:2" ht="15">
+      <c r="A396" s="3"/>
+      <c r="B396" s="3"/>
+    </row>
+    <row r="397" spans="1:2" ht="15">
+      <c r="A397" s="3"/>
+      <c r="B397" s="3"/>
+    </row>
+    <row r="398" spans="1:2" ht="15">
+      <c r="A398" s="3"/>
+      <c r="B398" s="3"/>
+    </row>
+    <row r="399" spans="1:2" ht="15">
+      <c r="A399" s="3"/>
+      <c r="B399" s="3"/>
+    </row>
+    <row r="400" spans="1:2" ht="15">
+      <c r="A400" s="3"/>
+      <c r="B400" s="3"/>
+    </row>
+    <row r="401" spans="1:2" ht="15">
+      <c r="A401" s="3"/>
+      <c r="B401" s="3"/>
+    </row>
+    <row r="402" spans="1:2" ht="15">
+      <c r="A402" s="3"/>
+      <c r="B402" s="3"/>
+    </row>
+    <row r="403" spans="1:2" ht="15">
+      <c r="A403" s="3"/>
+      <c r="B403" s="3"/>
+    </row>
+    <row r="404" spans="1:2" ht="15">
+      <c r="A404" s="3"/>
+      <c r="B404" s="3"/>
+    </row>
+    <row r="405" spans="1:2" ht="15">
+      <c r="A405" s="3"/>
+      <c r="B405" s="3"/>
+    </row>
+    <row r="406" spans="1:2" ht="15">
+      <c r="A406" s="3"/>
+      <c r="B406" s="3"/>
+    </row>
+    <row r="407" spans="1:2" ht="15">
+      <c r="A407" s="3"/>
+      <c r="B407" s="3"/>
+    </row>
+    <row r="408" spans="1:2" ht="15">
+      <c r="A408" s="3"/>
+      <c r="B408" s="3"/>
+    </row>
+    <row r="409" spans="1:2" ht="15">
+      <c r="A409" s="3"/>
+      <c r="B409" s="3"/>
+    </row>
+    <row r="410" spans="1:2" ht="15">
+      <c r="A410" s="3"/>
+      <c r="B410" s="3"/>
+    </row>
+    <row r="411" spans="1:2" ht="15">
+      <c r="A411" s="3"/>
+      <c r="B411" s="3"/>
+    </row>
+    <row r="412" spans="1:2" ht="15">
+      <c r="A412" s="3"/>
+      <c r="B412" s="3"/>
+    </row>
+    <row r="413" spans="1:2" ht="15">
+      <c r="A413" s="3"/>
+      <c r="B413" s="3"/>
+    </row>
+    <row r="414" spans="1:2" ht="15">
+      <c r="A414" s="3"/>
+      <c r="B414" s="3"/>
+    </row>
+    <row r="415" spans="1:2" ht="15">
+      <c r="A415" s="3"/>
+      <c r="B415" s="3"/>
+    </row>
+    <row r="416" spans="1:2" ht="15">
+      <c r="A416" s="3"/>
+      <c r="B416" s="3"/>
+    </row>
+    <row r="417" spans="1:2" ht="15">
+      <c r="A417" s="3"/>
+      <c r="B417" s="3"/>
+    </row>
+    <row r="418" spans="1:2" ht="15">
+      <c r="A418" s="3"/>
+      <c r="B418" s="3"/>
+    </row>
+    <row r="419" spans="1:2" ht="15">
+      <c r="A419" s="3"/>
+      <c r="B419" s="3"/>
+    </row>
+    <row r="420" spans="1:2" ht="15">
+      <c r="A420" s="3"/>
+      <c r="B420" s="3"/>
+    </row>
+    <row r="421" spans="1:2" ht="15">
+      <c r="A421" s="3"/>
+      <c r="B421" s="3"/>
+    </row>
+    <row r="422" spans="1:2" ht="15">
+      <c r="A422" s="3"/>
+      <c r="B422" s="3"/>
+    </row>
+    <row r="423" spans="1:2" ht="15">
+      <c r="A423" s="3"/>
+      <c r="B423" s="3"/>
+    </row>
+    <row r="424" spans="1:2" ht="15">
+      <c r="A424" s="3"/>
+      <c r="B424" s="3"/>
+    </row>
+    <row r="425" spans="1:2" ht="15">
+      <c r="A425" s="3"/>
+      <c r="B425" s="3"/>
+    </row>
+    <row r="426" spans="1:2" ht="15">
+      <c r="A426" s="3"/>
+      <c r="B426" s="3"/>
+    </row>
+    <row r="427" spans="1:2" ht="15">
+      <c r="A427" s="3"/>
+      <c r="B427" s="3"/>
+    </row>
+    <row r="428" spans="1:2" ht="15">
+      <c r="A428" s="3"/>
+      <c r="B428" s="3"/>
+    </row>
+    <row r="429" spans="1:2" ht="15">
+      <c r="A429" s="3"/>
+      <c r="B429" s="3"/>
+    </row>
+    <row r="430" spans="1:2" ht="15">
+      <c r="A430" s="3"/>
+      <c r="B430" s="3"/>
+    </row>
+    <row r="431" spans="1:2" ht="15">
+      <c r="A431" s="3"/>
+      <c r="B431" s="3"/>
+    </row>
+    <row r="432" spans="1:2" ht="15">
+      <c r="A432" s="3"/>
+      <c r="B432" s="3"/>
+    </row>
+    <row r="433" spans="1:2" ht="15">
+      <c r="A433" s="3"/>
+      <c r="B433" s="3"/>
+    </row>
+    <row r="434" spans="1:2" ht="15">
+      <c r="A434" s="3"/>
+      <c r="B434" s="3"/>
+    </row>
+    <row r="435" spans="1:2" ht="15">
+      <c r="A435" s="3"/>
+      <c r="B435" s="3"/>
+    </row>
+    <row r="436" spans="1:2" ht="15">
+      <c r="A436" s="3"/>
+      <c r="B436" s="3"/>
+    </row>
+    <row r="437" spans="1:2" ht="15">
+      <c r="A437" s="3"/>
+      <c r="B437" s="3"/>
+    </row>
+    <row r="438" spans="1:2" ht="15">
+      <c r="A438" s="3"/>
+      <c r="B438" s="3"/>
+    </row>
+    <row r="439" spans="1:2" ht="15">
+      <c r="A439" s="3"/>
+      <c r="B439" s="3"/>
+    </row>
+    <row r="440" spans="1:2" ht="15">
+      <c r="A440" s="3"/>
+      <c r="B440" s="3"/>
+    </row>
+    <row r="441" spans="1:2" ht="15">
+      <c r="A441" s="3"/>
+      <c r="B441" s="3"/>
+    </row>
+    <row r="442" spans="1:2" ht="15">
+      <c r="A442" s="3"/>
+      <c r="B442" s="3"/>
+    </row>
+    <row r="443" spans="1:2" ht="15">
+      <c r="A443" s="3"/>
+      <c r="B443" s="3"/>
+    </row>
+    <row r="444" spans="1:2" ht="15">
+      <c r="A444" s="3"/>
+      <c r="B444" s="3"/>
+    </row>
+    <row r="445" spans="1:2" ht="15">
+      <c r="A445" s="3"/>
+      <c r="B445" s="3"/>
+    </row>
+    <row r="446" spans="1:2" ht="15">
+      <c r="A446" s="3"/>
+      <c r="B446" s="3"/>
+    </row>
+    <row r="447" spans="1:2" ht="15">
+      <c r="A447" s="3"/>
+      <c r="B447" s="3"/>
+    </row>
+    <row r="448" spans="1:2" ht="15">
+      <c r="A448" s="3"/>
+      <c r="B448" s="3"/>
+    </row>
+    <row r="449" spans="1:2" ht="15">
+      <c r="A449" s="3"/>
+      <c r="B449" s="3"/>
+    </row>
+    <row r="450" spans="1:2" ht="15">
+      <c r="A450" s="3"/>
+      <c r="B450" s="3"/>
+    </row>
+    <row r="451" spans="1:2" ht="15">
+      <c r="A451" s="3"/>
+      <c r="B451" s="3"/>
+    </row>
+    <row r="452" spans="1:2" ht="15">
+      <c r="A452" s="3"/>
+      <c r="B452" s="3"/>
+    </row>
+    <row r="453" spans="1:2" ht="15">
+      <c r="A453" s="3"/>
+      <c r="B453" s="3"/>
+    </row>
+    <row r="454" spans="1:2" ht="15">
+      <c r="A454" s="3"/>
+      <c r="B454" s="3"/>
+    </row>
+    <row r="455" spans="1:2" ht="15">
+      <c r="A455" s="3"/>
+      <c r="B455" s="3"/>
+    </row>
+    <row r="456" spans="1:2" ht="15">
+      <c r="A456" s="3"/>
+      <c r="B456" s="3"/>
+    </row>
+    <row r="457" spans="1:2" ht="15">
+      <c r="A457" s="3"/>
+      <c r="B457" s="3"/>
+    </row>
+    <row r="458" spans="1:2" ht="15">
+      <c r="A458" s="3"/>
+      <c r="B458" s="3"/>
+    </row>
+    <row r="459" spans="1:2" ht="15">
+      <c r="A459" s="3"/>
+      <c r="B459" s="3"/>
+    </row>
+    <row r="460" spans="1:2" ht="15">
+      <c r="A460" s="3"/>
+      <c r="B460" s="3"/>
+    </row>
+    <row r="461" spans="1:2" ht="15">
+      <c r="A461" s="3"/>
+      <c r="B461" s="3"/>
+    </row>
+    <row r="462" spans="1:2" ht="15">
+      <c r="A462" s="3"/>
+      <c r="B462" s="3"/>
+    </row>
+    <row r="463" spans="1:2" ht="15">
+      <c r="A463" s="3"/>
+      <c r="B463" s="3"/>
+    </row>
+    <row r="464" spans="1:2" ht="15">
+      <c r="A464" s="3"/>
+      <c r="B464" s="3"/>
+    </row>
+    <row r="465" spans="1:2" ht="15">
+      <c r="A465" s="3"/>
+      <c r="B465" s="3"/>
+    </row>
+    <row r="466" spans="1:2" ht="15">
+      <c r="A466" s="3"/>
+      <c r="B466" s="3"/>
+    </row>
+    <row r="467" spans="1:2" ht="15">
+      <c r="A467" s="3"/>
+      <c r="B467" s="3"/>
+    </row>
+    <row r="468" spans="1:2" ht="15">
+      <c r="A468" s="3"/>
+      <c r="B468" s="3"/>
+    </row>
+    <row r="469" spans="1:2" ht="15">
+      <c r="A469" s="3"/>
+      <c r="B469" s="3"/>
+    </row>
+    <row r="470" spans="1:2" ht="15">
+      <c r="A470" s="3"/>
+      <c r="B470" s="3"/>
+    </row>
+    <row r="471" spans="1:2" ht="15">
+      <c r="A471" s="3"/>
+      <c r="B471" s="3"/>
+    </row>
+    <row r="472" spans="1:2" ht="15">
+      <c r="A472" s="3"/>
+      <c r="B472" s="3"/>
+    </row>
+    <row r="473" spans="1:2" ht="15">
+      <c r="A473" s="3"/>
+      <c r="B473" s="3"/>
+    </row>
+    <row r="474" spans="1:2" ht="15">
+      <c r="A474" s="3"/>
+      <c r="B474" s="3"/>
+    </row>
+    <row r="475" spans="1:2" ht="15">
+      <c r="A475" s="3"/>
+      <c r="B475" s="3"/>
+    </row>
+    <row r="476" spans="1:2" ht="15">
+      <c r="A476" s="3"/>
+      <c r="B476" s="3"/>
+    </row>
+    <row r="477" spans="1:2" ht="15">
+      <c r="A477" s="3"/>
+      <c r="B477" s="3"/>
+    </row>
+    <row r="478" spans="1:2" ht="15">
+      <c r="A478" s="3"/>
+      <c r="B478" s="3"/>
+    </row>
+    <row r="479" spans="1:2" ht="15">
+      <c r="A479" s="3"/>
+      <c r="B479" s="3"/>
+    </row>
+    <row r="480" spans="1:2" ht="15">
+      <c r="A480" s="3"/>
+      <c r="B480" s="3"/>
+    </row>
+    <row r="481" spans="1:2" ht="15">
+      <c r="A481" s="3"/>
+      <c r="B481" s="3"/>
+    </row>
+    <row r="482" spans="1:2" ht="15">
+      <c r="A482" s="3"/>
+      <c r="B482" s="3"/>
+    </row>
+    <row r="483" spans="1:2" ht="15">
+      <c r="A483" s="3"/>
+      <c r="B483" s="3"/>
+    </row>
+    <row r="484" spans="1:2" ht="15">
+      <c r="A484" s="3"/>
+      <c r="B484" s="3"/>
+    </row>
+    <row r="485" spans="1:2" ht="15">
+      <c r="A485" s="3"/>
+      <c r="B485" s="3"/>
+    </row>
+    <row r="486" spans="1:2" ht="15">
+      <c r="A486" s="3"/>
+      <c r="B486" s="3"/>
+    </row>
+    <row r="487" spans="1:2" ht="15">
+      <c r="A487" s="3"/>
+      <c r="B487" s="3"/>
+    </row>
+    <row r="488" spans="1:2" ht="15">
+      <c r="A488" s="3"/>
+      <c r="B488" s="3"/>
+    </row>
+    <row r="489" spans="1:2" ht="15">
+      <c r="A489" s="3"/>
+      <c r="B489" s="3"/>
+    </row>
+    <row r="490" spans="1:2" ht="15">
+      <c r="A490" s="3"/>
+      <c r="B490" s="3"/>
+    </row>
+    <row r="491" spans="1:2" ht="15">
+      <c r="A491" s="3"/>
+      <c r="B491" s="3"/>
+    </row>
+    <row r="492" spans="1:2" ht="15">
+      <c r="A492" s="3"/>
+      <c r="B492" s="3"/>
+    </row>
+    <row r="493" spans="1:2" ht="15">
+      <c r="A493" s="3"/>
+      <c r="B493" s="3"/>
+    </row>
+    <row r="494" spans="1:2" ht="15">
+      <c r="A494" s="3"/>
+      <c r="B494" s="3"/>
+    </row>
+    <row r="495" spans="1:2" ht="15">
+      <c r="A495" s="3"/>
+      <c r="B495" s="3"/>
+    </row>
+    <row r="496" spans="1:2" ht="15">
+      <c r="A496" s="3"/>
+      <c r="B496" s="3"/>
+    </row>
+    <row r="497" spans="1:2" ht="15">
+      <c r="A497" s="3"/>
+      <c r="B497" s="3"/>
+    </row>
+    <row r="498" spans="1:2" ht="15">
+      <c r="A498" s="3"/>
+      <c r="B498" s="3"/>
+    </row>
+    <row r="499" spans="1:2" ht="15">
+      <c r="A499" s="3"/>
+      <c r="B499" s="3"/>
+    </row>
+    <row r="500" spans="1:2" ht="15">
+      <c r="A500" s="3"/>
+      <c r="B500" s="3"/>
+    </row>
+    <row r="501" spans="1:2" ht="15">
+      <c r="A501" s="3"/>
+      <c r="B501" s="3"/>
+    </row>
+    <row r="502" spans="1:2" ht="15">
+      <c r="A502" s="3"/>
+      <c r="B502" s="3"/>
+    </row>
+    <row r="503" spans="1:2" ht="15">
+      <c r="A503" s="3"/>
+      <c r="B503" s="3"/>
+    </row>
+    <row r="504" spans="1:2" ht="15">
+      <c r="A504" s="3"/>
+      <c r="B504" s="3"/>
+    </row>
+    <row r="505" spans="1:2" ht="15">
+      <c r="A505" s="3"/>
+      <c r="B505" s="3"/>
+    </row>
+    <row r="506" spans="1:2" ht="15">
+      <c r="A506" s="3"/>
+      <c r="B506" s="3"/>
+    </row>
+    <row r="507" spans="1:2" ht="15">
+      <c r="A507" s="3"/>
+      <c r="B507" s="3"/>
+    </row>
+    <row r="508" spans="1:2" ht="15">
+      <c r="A508" s="3"/>
+      <c r="B508" s="3"/>
+    </row>
+    <row r="509" spans="1:2" ht="15">
+      <c r="A509" s="3"/>
+      <c r="B509" s="3"/>
+    </row>
+    <row r="510" spans="1:2" ht="15">
+      <c r="A510" s="3"/>
+      <c r="B510" s="3"/>
+    </row>
+    <row r="511" spans="1:2" ht="15">
+      <c r="A511" s="3"/>
+      <c r="B511" s="3"/>
+    </row>
+    <row r="512" spans="1:2" ht="15">
+      <c r="A512" s="3"/>
+      <c r="B512" s="3"/>
+    </row>
+    <row r="513" spans="1:2" ht="15">
+      <c r="A513" s="3"/>
+      <c r="B513" s="3"/>
+    </row>
+    <row r="514" spans="1:2" ht="15">
+      <c r="A514" s="3"/>
+      <c r="B514" s="3"/>
+    </row>
+    <row r="515" spans="1:2" ht="15">
+      <c r="A515" s="3"/>
+      <c r="B515" s="3"/>
+    </row>
+    <row r="516" spans="1:2" ht="15">
+      <c r="A516" s="3"/>
+      <c r="B516" s="3"/>
+    </row>
+    <row r="517" spans="1:2" ht="15">
+      <c r="A517" s="3"/>
+      <c r="B517" s="3"/>
+    </row>
+    <row r="518" spans="1:2" ht="15">
+      <c r="A518" s="3"/>
+      <c r="B518" s="3"/>
+    </row>
+    <row r="519" spans="1:2" ht="15">
+      <c r="A519" s="3"/>
+      <c r="B519" s="3"/>
+    </row>
+    <row r="520" spans="1:2" ht="15">
+      <c r="A520" s="3"/>
+      <c r="B520" s="3"/>
+    </row>
+    <row r="521" spans="1:2" ht="15">
+      <c r="A521" s="3"/>
+      <c r="B521" s="3"/>
+    </row>
+    <row r="522" spans="1:2" ht="15">
+      <c r="A522" s="3"/>
+      <c r="B522" s="3"/>
+    </row>
+    <row r="523" spans="1:2" ht="15">
+      <c r="A523" s="3"/>
+      <c r="B523" s="3"/>
+    </row>
+    <row r="524" spans="1:2" ht="15">
+      <c r="A524" s="3"/>
+      <c r="B524" s="3"/>
+    </row>
+    <row r="525" spans="1:2" ht="15">
+      <c r="A525" s="3"/>
+      <c r="B525" s="3"/>
+    </row>
+    <row r="526" spans="1:2" ht="15">
+      <c r="A526" s="3"/>
+      <c r="B526" s="3"/>
+    </row>
+    <row r="527" spans="1:2" ht="15">
+      <c r="A527" s="3"/>
+      <c r="B527" s="3"/>
+    </row>
+    <row r="528" spans="1:2" ht="15">
+      <c r="A528" s="3"/>
+      <c r="B528" s="3"/>
+    </row>
+    <row r="529" spans="1:2" ht="15">
+      <c r="A529" s="3"/>
+      <c r="B529" s="3"/>
+    </row>
+    <row r="530" spans="1:2" ht="15">
+      <c r="A530" s="3"/>
+      <c r="B530" s="3"/>
+    </row>
+    <row r="531" spans="1:2" ht="15">
+      <c r="A531" s="3"/>
+      <c r="B531" s="3"/>
+    </row>
+    <row r="532" spans="1:2" ht="15">
+      <c r="A532" s="3"/>
+      <c r="B532" s="3"/>
+    </row>
+    <row r="533" spans="1:2" ht="15">
+      <c r="A533" s="3"/>
+      <c r="B533" s="3"/>
+    </row>
+    <row r="534" spans="1:2" ht="15">
+      <c r="A534" s="3"/>
+      <c r="B534" s="3"/>
+    </row>
+    <row r="535" spans="1:2" ht="15">
+      <c r="A535" s="3"/>
+      <c r="B535" s="3"/>
+    </row>
+    <row r="536" spans="1:2" ht="15">
+      <c r="A536" s="3"/>
+      <c r="B536" s="3"/>
+    </row>
+    <row r="537" spans="1:2" ht="15">
+      <c r="A537" s="3"/>
+      <c r="B537" s="3"/>
+    </row>
+    <row r="538" spans="1:2" ht="15">
+      <c r="A538" s="3"/>
+      <c r="B538" s="3"/>
+    </row>
+    <row r="539" spans="1:2" ht="15">
+      <c r="A539" s="3"/>
+      <c r="B539" s="3"/>
+    </row>
+    <row r="540" spans="1:2" ht="15">
+      <c r="A540" s="3"/>
+      <c r="B540" s="3"/>
+    </row>
+    <row r="541" spans="1:2" ht="15">
+      <c r="A541" s="3"/>
+      <c r="B541" s="3"/>
+    </row>
+    <row r="542" spans="1:2" ht="15">
+      <c r="A542" s="3"/>
+      <c r="B542" s="3"/>
+    </row>
+    <row r="543" spans="1:2" ht="15">
+      <c r="A543" s="3"/>
+      <c r="B543" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Regularizar.xlsx
+++ b/Treinamento/Planilha Robô Regularizar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28521"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28528"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="268" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{804B0DE8-F9C7-4C8D-BDB4-3D47F4989FE1}"/>
+  <xr:revisionPtr revIDLastSave="272" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1230EEA3-9180-432A-90A5-F3586F92640A}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="4">
   <si>
     <t>Recibo</t>
   </si>
@@ -470,7 +470,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>747600330</v>
+        <v>636344941</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -478,7 +478,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>646707673</v>
+        <v>672614124</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -486,7 +486,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>732809540</v>
+        <v>709530525</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -494,7 +494,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>737499289</v>
+        <v>683563559</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -502,7 +502,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>737492268</v>
+        <v>682327105</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -510,7 +510,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>736673637</v>
+        <v>656092966</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -518,7 +518,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>726732708</v>
+        <v>651809711</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>726732690</v>
+        <v>636255642</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>2</v>
@@ -534,7 +534,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>677566980</v>
+        <v>614420424</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>2</v>
@@ -542,7 +542,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>675809887</v>
+        <v>623325077</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -550,7 +550,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>668998572</v>
+        <v>604617120</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>657358168</v>
+        <v>597255854</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -566,7 +566,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>649321928</v>
+        <v>557521857</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -574,7 +574,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>611821624</v>
+        <v>594464806</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
@@ -582,7 +582,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>630952913</v>
+        <v>582564468</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
@@ -590,79 +590,79 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>632987842</v>
+        <v>601401288</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>627209343</v>
+        <v>668106614</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>625605955</v>
+        <v>740766344</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>608909929</v>
+        <v>741056166</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>605216187</v>
+        <v>737354104</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>602168936</v>
+        <v>719923967</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>597430473</v>
+        <v>719638599</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>596170047</v>
+        <v>717006542</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>591222512</v>
+        <v>716688647</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>563921323</v>
+        <v>715094045</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>3</v>
@@ -670,7 +670,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>746220874</v>
+        <v>708181015</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>3</v>
@@ -678,7 +678,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>740615491</v>
+        <v>703560205</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>3</v>
@@ -686,7 +686,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>671502478</v>
+        <v>702092044</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>3</v>
@@ -694,7 +694,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>714434507</v>
+        <v>702023130</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>3</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>738338270</v>
+        <v>699928234</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>3</v>
@@ -710,7 +710,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>701009239</v>
+        <v>696660806</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>3</v>
@@ -718,7 +718,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>686508759</v>
+        <v>691243368</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>3</v>
@@ -726,7 +726,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>677239968</v>
+        <v>636462552</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>3</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>620056790</v>
+        <v>667694420</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>3</v>
@@ -742,7 +742,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>634008068</v>
+        <v>666566769</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>3</v>
@@ -750,14 +750,19 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>630242968</v>
+        <v>628511432</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="B38" s="4"/>
+      <c r="A38">
+        <v>610074043</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39" spans="1:2">
       <c r="B39" s="4"/>

--- a/Treinamento/Planilha Robô Regularizar.xlsx
+++ b/Treinamento/Planilha Robô Regularizar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="272" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1230EEA3-9180-432A-90A5-F3586F92640A}"/>
+  <xr:revisionPtr revIDLastSave="276" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDD4B38A-D185-4CE5-BDAE-85E374E4211B}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="4">
   <si>
     <t>Recibo</t>
   </si>
@@ -470,7 +470,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>636344941</v>
+        <v>630295560</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -478,7 +478,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>672614124</v>
+        <v>671408460</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -486,7 +486,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>709530525</v>
+        <v>747629578</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -494,7 +494,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>683563559</v>
+        <v>736525944</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -502,7 +502,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>682327105</v>
+        <v>725389625</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -510,7 +510,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>656092966</v>
+        <v>704686074</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -518,7 +518,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>651809711</v>
+        <v>694075254</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>636255642</v>
+        <v>692686029</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>2</v>
@@ -534,7 +534,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>614420424</v>
+        <v>676472917</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>2</v>
@@ -542,7 +542,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>623325077</v>
+        <v>655619132</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -550,7 +550,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>604617120</v>
+        <v>649734484</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>597255854</v>
+        <v>649730409</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -566,7 +566,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>557521857</v>
+        <v>641829084</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -574,7 +574,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>594464806</v>
+        <v>639626013</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
@@ -582,7 +582,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>582564468</v>
+        <v>628103818</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
@@ -590,167 +590,167 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>601401288</v>
+        <v>627767142</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>668106614</v>
+        <v>626229946</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>740766344</v>
+        <v>623895285</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>741056166</v>
+        <v>623174640</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>737354104</v>
+        <v>620849004</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>719923967</v>
+        <v>618087229</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>719638599</v>
+        <v>606973034</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>717006542</v>
+        <v>607511056</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>716688647</v>
+        <v>588113914</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>715094045</v>
+        <v>583616440</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>708181015</v>
+        <v>580392748</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>703560205</v>
+        <v>578102323</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>702092044</v>
+        <v>174760953</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>702023130</v>
+        <v>577950763</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>699928234</v>
+        <v>574340992</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>696660806</v>
+        <v>561248836</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>691243368</v>
+        <v>560433595</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>636462552</v>
+        <v>560389060</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>667694420</v>
+        <v>548949035</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>666566769</v>
+        <v>171118528</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>628511432</v>
+        <v>744331251</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>3</v>
@@ -758,20 +758,35 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>610074043</v>
+        <v>740364595</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="B39" s="4"/>
+      <c r="A39">
+        <v>617230606</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="B40" s="4"/>
+      <c r="A40">
+        <v>634544351</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="B41" s="4"/>
+      <c r="A41">
+        <v>621539661</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="42" spans="1:2">
       <c r="B42" s="4"/>

--- a/Treinamento/Planilha Robô Regularizar.xlsx
+++ b/Treinamento/Planilha Robô Regularizar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28528"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28602"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="276" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDD4B38A-D185-4CE5-BDAE-85E374E4211B}"/>
+  <xr:revisionPtr revIDLastSave="280" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC33DE68-05E1-4604-80BD-9620C9C9868A}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="4">
   <si>
     <t>Recibo</t>
   </si>
@@ -470,7 +470,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>630295560</v>
+        <v>700924198</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -478,7 +478,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>671408460</v>
+        <v>642608065</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -486,7 +486,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>747629578</v>
+        <v>635835816</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -494,7 +494,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>736525944</v>
+        <v>618582310</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -502,7 +502,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>725389625</v>
+        <v>631883109</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -510,7 +510,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>704686074</v>
+        <v>633670124</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -518,7 +518,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>694075254</v>
+        <v>631854159</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>692686029</v>
+        <v>617488089</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>2</v>
@@ -534,7 +534,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>676472917</v>
+        <v>544401072</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>2</v>
@@ -542,7 +542,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>655619132</v>
+        <v>572511263</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -550,7 +550,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>649734484</v>
+        <v>615159658</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>649730409</v>
+        <v>607817016</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -566,7 +566,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>641829084</v>
+        <v>607014234</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -574,7 +574,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>639626013</v>
+        <v>597053176</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
@@ -582,7 +582,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>628103818</v>
+        <v>593312816</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>627767142</v>
+        <v>592185825</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -598,7 +598,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>626229946</v>
+        <v>589299241</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
@@ -606,7 +606,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>623895285</v>
+        <v>579760111</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -614,7 +614,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>623174640</v>
+        <v>575210590</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>2</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>620849004</v>
+        <v>563253107</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>2</v>
@@ -630,7 +630,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>618087229</v>
+        <v>736526785</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>2</v>
@@ -638,7 +638,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>606973034</v>
+        <v>712397763</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2</v>
@@ -646,7 +646,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>607511056</v>
+        <v>688590953</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>2</v>
@@ -654,7 +654,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>588113914</v>
+        <v>672565359</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2</v>
@@ -662,7 +662,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>583616440</v>
+        <v>682906908</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>2</v>
@@ -670,7 +670,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>580392748</v>
+        <v>686898663</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>2</v>
@@ -678,7 +678,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>578102323</v>
+        <v>686011549</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2</v>
@@ -686,71 +686,71 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>174760953</v>
+        <v>685936670</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>577950763</v>
+        <v>616882993</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>574340992</v>
+        <v>633889666</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>561248836</v>
+        <v>650656220</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>560433595</v>
+        <v>656211533</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>560389060</v>
+        <v>629982988</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>548949035</v>
+        <v>628100780</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>171118528</v>
+        <v>623051467</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>744331251</v>
+        <v>741928398</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>3</v>
@@ -758,7 +758,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>740364595</v>
+        <v>745813034</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>3</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>617230606</v>
+        <v>745778906</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>3</v>
@@ -774,7 +774,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>634544351</v>
+        <v>741399483</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>3</v>
@@ -782,20 +782,59 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>621539661</v>
+        <v>722324583</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="B42" s="4"/>
+      <c r="A42">
+        <v>725884468</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="B43" s="4"/>
+      <c r="A43">
+        <v>693327581</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="B44" s="4"/>
+      <c r="A44">
+        <v>714023888</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>708938794</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>684500311</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>678156187</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="147" spans="1:2" ht="15">
       <c r="A147" s="3"/>

--- a/Treinamento/Planilha Robô Regularizar.xlsx
+++ b/Treinamento/Planilha Robô Regularizar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28605"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="284" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6DFE24A-BABB-4069-B957-F3AAA7822E0F}"/>
+  <xr:revisionPtr revIDLastSave="288" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E3749DA-2B3D-40B3-B18F-985E5C1FEB70}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="4">
   <si>
     <t>Recibo</t>
   </si>
@@ -143,7 +143,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -476,7 +481,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>566256594</v>
+        <v>676488236</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -484,7 +489,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>752461206</v>
+        <v>743349957</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -492,7 +497,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>665638155</v>
+        <v>715868406</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -500,7 +505,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>698281502</v>
+        <v>715290882</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -508,7 +513,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>719722385</v>
+        <v>689763179</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -516,7 +521,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>723039768</v>
+        <v>677084513</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -524,7 +529,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>726467040</v>
+        <v>667889152</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -532,7 +537,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>701095642</v>
+        <v>650464062</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>2</v>
@@ -540,7 +545,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>698942483</v>
+        <v>647505365</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>2</v>
@@ -548,7 +553,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>694912159</v>
+        <v>644577714</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -556,7 +561,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>682907260</v>
+        <v>626113991</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -564,7 +569,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>692157435</v>
+        <v>629593561</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -572,7 +577,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>636109070</v>
+        <v>637357934</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -580,7 +585,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>648223299</v>
+        <v>630830028</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
@@ -588,7 +593,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>659115657</v>
+        <v>617348085</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
@@ -596,7 +601,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>630950842</v>
+        <v>617141928</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -604,7 +609,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>630307548</v>
+        <v>606486730</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
@@ -612,7 +617,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>629178348</v>
+        <v>605325186</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -620,7 +625,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>628549465</v>
+        <v>602607859</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>2</v>
@@ -628,7 +633,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>607883281</v>
+        <v>601077773</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>2</v>
@@ -636,7 +641,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>607530015</v>
+        <v>571184872</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>2</v>
@@ -644,7 +649,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>605969686</v>
+        <v>566495986</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2</v>
@@ -652,7 +657,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>596962856</v>
+        <v>171763836</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>2</v>
@@ -660,7 +665,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>596852685</v>
+        <v>174616783</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2</v>
@@ -668,39 +673,39 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>595495510</v>
+        <v>745789853</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>593264520</v>
+        <v>746027832</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>573086745</v>
+        <v>702772835</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>565525213</v>
+        <v>742646270</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>750634689</v>
+        <v>656603846</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>3</v>
@@ -708,235 +713,95 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>745540983</v>
+        <v>675615029</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32">
-        <v>660141841</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>675101236</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>608333070</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
-        <v>627847498</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>616088690</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>628486833</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>736525571</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>753577745</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>666089457</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
-        <v>713703365</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>731422923</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
-        <v>731422741</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
-        <v>650006152</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>649841511</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>638504286</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
-        <v>638287346</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48">
-        <v>633759893</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>612241301</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>606728933</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>596909212</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
-        <v>594931952</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
-        <v>545911285</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54">
-        <v>549713281</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55">
-        <v>746434707</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56">
-        <v>751696471</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57">
-        <v>715251942</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58">
-        <v>693966487</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59">
-        <v>697144446</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="B32" s="4"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="4"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="4"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="4"/>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="4"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="4"/>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="4"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="4"/>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="4"/>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="4"/>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="4"/>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="4"/>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="4"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="4"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="4"/>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="4"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="4"/>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="4"/>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="4"/>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="4"/>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="4"/>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="4"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="4"/>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="4"/>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="4"/>
     </row>
     <row r="147" spans="1:2" ht="15">
       <c r="A147" s="3"/>
@@ -2527,7 +2392,10 @@
       <c r="B543" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A59">
+  <conditionalFormatting sqref="A32:A59">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A31">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Regularizar.xlsx
+++ b/Treinamento/Planilha Robô Regularizar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="306" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ECC815E-B916-42F3-AA74-07AA2A8E3BC0}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63746483-3EDA-4BCC-8033-8B502869E1B5}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
@@ -469,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDA9D80-CE6D-4C1A-B019-EB3A00964886}">
-  <dimension ref="A1:B543"/>
+  <dimension ref="A1:H543"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -486,7 +489,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>658838614</v>
+        <v>558413666</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -494,7 +497,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>752811046</v>
+        <v>700912714</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -502,7 +505,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>737461479</v>
+        <v>678330857</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -510,7 +513,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>737085500</v>
+        <v>687008957</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -518,7 +521,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>723687129</v>
+        <v>662304157</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -526,7 +529,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>704942345</v>
+        <v>650338266</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -534,7 +537,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>704239916</v>
+        <v>649296351</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -542,7 +545,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>655087033</v>
+        <v>645281035</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>2</v>
@@ -550,7 +553,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>643415353</v>
+        <v>633693563</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>2</v>
@@ -558,7 +561,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>649349671</v>
+        <v>639009236</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -566,7 +569,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>640995936</v>
+        <v>636071049</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -574,7 +577,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>637828579</v>
+        <v>635907623</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -582,7 +585,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>633472067</v>
+        <v>633164037</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -590,7 +593,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>627855350</v>
+        <v>630574188</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
@@ -598,186 +601,194 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>556317471</v>
+        <v>624164772</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:8">
       <c r="A17">
-        <v>626957082</v>
+        <v>629627179</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="H17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18">
-        <v>625788363</v>
+        <v>618009793</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:8">
       <c r="A19">
-        <v>610186466</v>
+        <v>617939024</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:8">
       <c r="A20">
-        <v>585464047</v>
+        <v>617018282</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:8">
       <c r="A21">
-        <v>571993488</v>
+        <v>611939194</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:8">
       <c r="A22">
-        <v>571993470</v>
+        <v>593835345</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:8">
       <c r="A23">
-        <v>566689331</v>
+        <v>607332487</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:8">
       <c r="A24">
-        <v>559781285</v>
+        <v>605084239</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:8">
       <c r="A25">
-        <v>174761712</v>
+        <v>602095105</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:8">
       <c r="A26">
-        <v>613631153</v>
+        <v>602051512</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27">
-        <v>748032293</v>
+        <v>570746978</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28">
-        <v>755659418</v>
+        <v>536331881</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29">
-        <v>750637674</v>
+        <v>172303939</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30">
-        <v>751641428</v>
+        <v>169545344</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31">
-        <v>751358700</v>
+        <v>739611063</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32">
-        <v>750956728</v>
+        <v>758859346</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="4"/>
-    </row>
-    <row r="34" spans="2:2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>588737084</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="B34" s="4"/>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="1:2">
       <c r="B35" s="4"/>
     </row>
-    <row r="36" spans="2:2">
+    <row r="36" spans="1:2">
       <c r="B36" s="4"/>
     </row>
-    <row r="37" spans="2:2">
+    <row r="37" spans="1:2">
       <c r="B37" s="4"/>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="1:2">
       <c r="B38" s="4"/>
     </row>
-    <row r="39" spans="2:2">
+    <row r="39" spans="1:2">
       <c r="B39" s="4"/>
     </row>
-    <row r="40" spans="2:2">
+    <row r="40" spans="1:2">
       <c r="B40" s="4"/>
     </row>
-    <row r="41" spans="2:2">
+    <row r="41" spans="1:2">
       <c r="B41" s="4"/>
     </row>
-    <row r="42" spans="2:2">
+    <row r="42" spans="1:2">
       <c r="B42" s="4"/>
     </row>
-    <row r="43" spans="2:2">
+    <row r="43" spans="1:2">
       <c r="B43" s="4"/>
     </row>
-    <row r="44" spans="2:2">
+    <row r="44" spans="1:2">
       <c r="B44" s="4"/>
     </row>
-    <row r="45" spans="2:2">
+    <row r="45" spans="1:2">
       <c r="B45" s="4"/>
     </row>
-    <row r="46" spans="2:2">
+    <row r="46" spans="1:2">
       <c r="B46" s="4"/>
     </row>
-    <row r="47" spans="2:2">
+    <row r="47" spans="1:2">
       <c r="B47" s="4"/>
     </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="1:2">
       <c r="B48" s="4"/>
     </row>
     <row r="49" spans="2:2">
@@ -2424,12 +2435,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A66">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A33:A65">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="A34:A65">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A32">
+  <conditionalFormatting sqref="A2:A33">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Regularizar.xlsx
+++ b/Treinamento/Planilha Robô Regularizar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03855-R0260610\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="311" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63746483-3EDA-4BCC-8033-8B502869E1B5}"/>
+  <xr:revisionPtr revIDLastSave="317" documentId="13_ncr:1_{1A04E817-1771-4A87-A6E2-94246EA070AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D304E26-FB7B-42A4-BDA6-8D2B46CEADD3}"/>
   <bookViews>
     <workbookView xWindow="1650" yWindow="-120" windowWidth="18960" windowHeight="11760" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,12 +36,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="6">
   <si>
     <t>Recibo</t>
   </si>
   <si>
     <t xml:space="preserve">OCORRENCIA_INTERNA                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
@@ -146,7 +149,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -489,7 +497,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>558413666</v>
+        <v>669920666</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -497,7 +505,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>700912714</v>
+        <v>694650502</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -505,7 +513,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>678330857</v>
+        <v>690139328</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -513,7 +521,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>687008957</v>
+        <v>694605753</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -521,7 +529,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>662304157</v>
+        <v>717807881</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -529,7 +537,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>650338266</v>
+        <v>596113427</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -537,7 +545,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>649296351</v>
+        <v>743562179</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -545,7 +553,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>645281035</v>
+        <v>745152649</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>2</v>
@@ -553,7 +561,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>633693563</v>
+        <v>631774613</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>2</v>
@@ -561,7 +569,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>639009236</v>
+        <v>721346769</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -569,7 +577,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>636071049</v>
+        <v>681140863</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -577,192 +585,222 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>635907623</v>
+        <v>659343267</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>633164037</v>
+        <v>721311854</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>630574188</v>
+        <v>740060060</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>624164772</v>
+        <v>716756865</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>629627179</v>
+        <v>680535725</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>618009793</v>
+        <v>682907153</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>617939024</v>
+        <v>652355581</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>617018282</v>
+        <v>626004620</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>611939194</v>
+        <v>642512515</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>593835345</v>
+        <v>647512304</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>607332487</v>
+        <v>650085578</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>605084239</v>
+        <v>636129524</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>602095105</v>
+        <v>607565334</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>602051512</v>
+        <v>624765891</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>570746978</v>
+        <v>623229261</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>536331881</v>
+        <v>593081841</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>172303939</v>
+        <v>591222520</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>169545344</v>
+        <v>573158023</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>739611063</v>
+        <v>572033474</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>758859346</v>
+        <v>570491997</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>588737084</v>
+        <v>569711942</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="B34" s="4"/>
+      <c r="A34">
+        <v>548496771</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="B35" s="4"/>
+      <c r="A35">
+        <v>560113593</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="B36" s="4"/>
+      <c r="A36">
+        <v>558282897</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="B37" s="4"/>
+      <c r="A37">
+        <v>171864014</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="B38" s="4"/>
+      <c r="A38">
+        <v>171142882</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="B39" s="4"/>
+      <c r="A39">
+        <v>623895293</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="40" spans="1:2">
       <c r="B40" s="4"/>
@@ -2435,12 +2473,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A66">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A34:A65">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  <conditionalFormatting sqref="A40:A65">
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A33">
+  <conditionalFormatting sqref="A2:A12">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13:A39">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Planilha Robô Regularizar.xlsx
+++ b/Treinamento/Planilha Robô Regularizar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03856-R0260586\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2043E4-308A-4C14-9001-D384019FC855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9552BC6A-9515-44E3-8F7F-FD6B8868E0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5941E9CA-B087-4FE8-B1CB-F0F427193C50}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="5">
   <si>
     <t>Recibo</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
 </sst>
 </file>
@@ -143,7 +146,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -481,7 +489,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>693988507</v>
+        <v>738022692</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -489,7 +497,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>686743117</v>
+        <v>753785975</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -497,7 +505,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>690494186</v>
+        <v>767112612</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
@@ -505,7 +513,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>687502546</v>
+        <v>750928974</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -513,7 +521,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>685612156</v>
+        <v>743041208</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -521,7 +529,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>682487883</v>
+        <v>742883741</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -529,7 +537,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>680128224</v>
+        <v>722303249</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -537,7 +545,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>674779404</v>
+        <v>722286865</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>2</v>
@@ -545,7 +553,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>674740349</v>
+        <v>685893079</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>2</v>
@@ -553,7 +561,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>667987063</v>
+        <v>704291370</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>2</v>
@@ -561,7 +569,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>665608505</v>
+        <v>709600518</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -569,7 +577,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>665603159</v>
+        <v>703204044</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -577,7 +585,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>650863164</v>
+        <v>693881116</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -585,7 +593,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>657926105</v>
+        <v>699732636</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
@@ -593,7 +601,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>663671679</v>
+        <v>695495071</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
@@ -601,7 +609,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>662995590</v>
+        <v>689087280</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -609,7 +617,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>661599534</v>
+        <v>691463156</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
@@ -617,7 +625,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>808863231</v>
+        <v>687165419</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -625,7 +633,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>801995246</v>
+        <v>688442767</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>2</v>
@@ -633,7 +641,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>800420519</v>
+        <v>688279664</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>2</v>
@@ -641,7 +649,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>770181984</v>
+        <v>673833079</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>2</v>
@@ -649,7 +657,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>770842627</v>
+        <v>678491402</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2</v>
@@ -657,7 +665,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>595732193</v>
+        <v>672824301</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>2</v>
@@ -665,7 +673,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>173233499</v>
+        <v>647791379</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2</v>
@@ -673,7 +681,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>719825535</v>
+        <v>653649164</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>2</v>
@@ -681,7 +689,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>762343519</v>
+        <v>665517284</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>2</v>
@@ -689,7 +697,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>762254773</v>
+        <v>670490865</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2</v>
@@ -697,7 +705,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>734005410</v>
+        <v>659009645</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>2</v>
@@ -705,7 +713,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>743093308</v>
+        <v>653170286</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>2</v>
@@ -713,7 +721,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>722239161</v>
+        <v>649763327</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>2</v>
@@ -721,7 +729,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>733687036</v>
+        <v>637948963</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>2</v>
@@ -729,7 +737,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>731508382</v>
+        <v>637828587</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>2</v>
@@ -737,7 +745,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>730818923</v>
+        <v>631251067</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>2</v>
@@ -745,7 +753,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>709880193</v>
+        <v>625112135</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>2</v>
@@ -753,7 +761,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>704059009</v>
+        <v>625023910</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>2</v>
@@ -761,184 +769,279 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>714751736</v>
+        <v>617232313</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>787997893</v>
+        <v>614576837</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>800519757</v>
+        <v>807940378</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>803080260</v>
+        <v>798119222</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>801209283</v>
+        <v>777420484</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>800126116</v>
+        <v>781008408</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>810609093</v>
+        <v>789380999</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>693327607</v>
+        <v>780875310</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>699119743</v>
+        <v>773069871</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>768699245</v>
+        <v>811695604</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B47" s="4"/>
+      <c r="A47">
+        <v>611409693</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B48" s="4"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B49" s="4"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B50" s="4"/>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B51" s="4"/>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B52" s="4"/>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B53" s="4"/>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B54" s="4"/>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B55" s="4"/>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B56" s="4"/>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B57" s="4"/>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B58" s="4"/>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B59" s="4"/>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B60" s="4"/>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B61" s="4"/>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B62" s="4"/>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B63" s="4"/>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B64" s="4"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B65" s="4"/>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>608713644</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>606835761</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>813692906</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>812269011</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>812094013</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>812006835</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>811770100</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>810910210</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>809275484</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>802626568</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>805917907</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>796899353</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>775644713</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>736468178</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>770225708</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>177147018</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>676598737</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>676598737</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B66" s="4"/>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B67" s="4"/>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B68" s="4"/>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B69" s="4"/>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B70" s="4"/>
     </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B71" s="4"/>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B72" s="4"/>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B73" s="4"/>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B74" s="4"/>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B75" s="4"/>
     </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B76" s="4"/>
     </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B77" s="4"/>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B78" s="4"/>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B79" s="4"/>
     </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B80" s="4"/>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
@@ -2059,10 +2162,10 @@
       <c r="B361" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A47:A87">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="A66:A87">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A46">
+  <conditionalFormatting sqref="A2:A65">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
